--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5646" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="788">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-patient</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-patient</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -543,7 +543,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>1954: fixed value without value? case not xsi:nil</t>
+    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native when ADERS - 24_PtRace_AIAN (A-24.1) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:ombCategory.id</t>
@@ -604,7 +604,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1952-1: fixed value = urn:oid:2.16.840.1.113883.6.238#2106-3 WHITE case not xsi:nil</t>
+    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race when ADERS - 24_PtRace_Other (A-24.7) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:detailed</t>
@@ -702,9 +702,6 @@
     <t>Patient.extension:ethnicity.extension:ombCategory</t>
   </si>
   <si>
-    <t>1958: fixed value without value? case not xsi:nil</t>
-  </si>
-  <si>
     <t>Patient.extension:ethnicity.extension:ombCategory.id</t>
   </si>
   <si>
@@ -718,6 +715,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category</t>
+  </si>
+  <si>
+    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#ASKU asked but unknown when ADERS - 25_PtEthnicity_Other (A-25.4) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:detailed</t>
@@ -831,7 +831,7 @@
     <t>Patient.extension:patient-ageAtVaccination.value[x]</t>
   </si>
   <si>
-    <t>1882: transform using concat(6_PtAgeVacYears, 6_PtAgeVacMonths)</t>
+    <t>1882: transform using concat(6_PtAgeVacYears, 6_PtAgeVacMonths) on ADERS - (A-)</t>
   </si>
   <si>
     <t>Patient.extension:us-core-race</t>
@@ -1636,7 +1636,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
   </si>
   <si>
-    <t>1880: source value from ADERS - 3_ptSex</t>
+    <t>1880: source value from ADERS - 3_ptSex (A-3)</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1664,7 +1664,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>1874: source value from ADERS - 2_ptDOB</t>
+    <t>1874: source value from ADERS - 2_ptDOB (A-2)</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1717,7 +1717,7 @@
     <t>deceasedBoolean</t>
   </si>
   <si>
-    <t>1916: source value from ADERS - 21_Death case 21_DeathDt nil &amp; 21_Death =1</t>
+    <t>1916: source value from ADERS - 21_Death (A-21.6) case 21_DeathDt nil &amp; 21_Death =1</t>
   </si>
   <si>
     <t>Patient.deceased[x]:deceasedDateTime</t>
@@ -1730,7 +1730,7 @@
 </t>
   </si>
   <si>
-    <t>1917: source value from ADERS - 21_DeathDt case 21_DeathDt NOT nil</t>
+    <t>1917: source value from ADERS - 21_DeathDt (A-21.7) case 21_DeathDt NOT nil</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2809,7 +2809,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="149.140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>
@@ -6836,7 +6836,7 @@
         <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>169</v>
@@ -6980,21 +6980,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>171</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -7009,14 +7009,12 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -7086,7 +7084,7 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>83</v>
@@ -7103,7 +7101,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>173</v>
@@ -7226,7 +7224,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>179</v>
@@ -7243,7 +7241,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>83</v>
@@ -7289,7 +7287,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7322,7 +7320,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native when ADERS - 24_PtRace_AIAN (A-24.1) case not xsi:nil</t>
+    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native when ADERS - PtRace_AIAN (A-24.1) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:ombCategory.id</t>
@@ -604,7 +604,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race when ADERS - 24_PtRace_Other (A-24.7) case not xsi:nil</t>
+    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race when ADERS - PtRace_Other (A-24.7) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:detailed</t>
@@ -717,7 +717,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category</t>
   </si>
   <si>
-    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#ASKU asked but unknown when ADERS - 25_PtEthnicity_Other (A-25.4) case not xsi:nil</t>
+    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH other when ADERS - PtEthnicity_Other (A-25.4) case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:detailed</t>
@@ -878,7 +878,7 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t>1863: source value from ADERS - 0_Pt_ICN_Full</t>
+    <t>1863: source value from ADERS - Pt_ICN_Full (A-0)</t>
   </si>
   <si>
     <t>id</t>
@@ -1636,7 +1636,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
   </si>
   <si>
-    <t>1880: source value from ADERS - 3_ptSex (A-3)</t>
+    <t>1880: source value from ADERS - ptSex (A-3)</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1664,7 +1664,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>1874: source value from ADERS - 2_ptDOB (A-2)</t>
+    <t>1874: source value from ADERS - ptDOB (A-2)</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1717,7 +1717,7 @@
     <t>deceasedBoolean</t>
   </si>
   <si>
-    <t>1916: source value from ADERS - 21_Death (A-21.6) case 21_DeathDt nil &amp; 21_Death =1</t>
+    <t>1916: source value from ADERS - Death (A-21.6) case 21_DeathDt nil &amp; 21_Death =1</t>
   </si>
   <si>
     <t>Patient.deceased[x]:deceasedDateTime</t>
@@ -1730,7 +1730,7 @@
 </t>
   </si>
   <si>
-    <t>1917: source value from ADERS - 21_DeathDt (A-21.7) case 21_DeathDt NOT nil</t>
+    <t>1917: source value from ADERS - DeathDt (A-21.7) case 21_DeathDt NOT nil</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2809,7 +2809,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="149.140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="137.55859375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native when ADERS - PtRace_AIAN (A-24.1) case not xsi:nil</t>
+    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:ombCategory.id</t>
@@ -604,7 +604,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race when ADERS - PtRace_Other (A-24.7) case not xsi:nil</t>
+    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:detailed</t>
@@ -717,7 +717,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category</t>
   </si>
   <si>
-    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH other when ADERS - PtEthnicity_Other (A-25.4) case not xsi:nil</t>
+    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH other case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:detailed</t>
@@ -831,7 +831,7 @@
     <t>Patient.extension:patient-ageAtVaccination.value[x]</t>
   </si>
   <si>
-    <t>1882: transform using concat(6_PtAgeVacYears, 6_PtAgeVacMonths) on ADERS - (A-)</t>
+    <t>1882: transform using concat(6_PtAgeVacYears, 6_PtAgeVacMonths)</t>
   </si>
   <si>
     <t>Patient.extension:us-core-race</t>
@@ -878,7 +878,7 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t>1863: source value from ADERS - Pt_ICN_Full (A-0)</t>
+    <t>1863: source value from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>id</t>
@@ -1636,7 +1636,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
   </si>
   <si>
-    <t>1880: source value from ADERS - ptSex (A-3)</t>
+    <t>1880: source value from ADERS - 3_ptSex</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1664,7 +1664,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>1874: source value from ADERS - ptDOB (A-2)</t>
+    <t>1874: source value from ADERS - 2_ptDOB</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1717,7 +1717,7 @@
     <t>deceasedBoolean</t>
   </si>
   <si>
-    <t>1916: source value from ADERS - Death (A-21.6) case 21_DeathDt nil &amp; 21_Death =1</t>
+    <t>1916: source value from ADERS - 21_Death case 21_DeathDt nil &amp; 21_Death =1</t>
   </si>
   <si>
     <t>Patient.deceased[x]:deceasedDateTime</t>
@@ -1730,7 +1730,7 @@
 </t>
   </si>
   <si>
-    <t>1917: source value from ADERS - DeathDt (A-21.7) case 21_DeathDt NOT nil</t>
+    <t>1917: source value from ADERS - 21_DeathDt case 21_DeathDt NOT nil</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2809,7 +2809,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="137.55859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="103.6484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$142</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="784">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -832,18 +832,6 @@
   </si>
   <si>
     <t>1882: transform using concat(6_PtAgeVacYears, 6_PtAgeVacMonths)</t>
-  </si>
-  <si>
-    <t>Patient.extension:us-core-race</t>
-  </si>
-  <si>
-    <t>us-core-race</t>
-  </si>
-  <si>
-    <t>Patient.extension:us-core-ethnicity</t>
-  </si>
-  <si>
-    <t>us-core-ethnicity</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -2771,7 +2759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ144"/>
+  <dimension ref="A1:AQ142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.8515625" customWidth="true" bestFit="true"/>
@@ -9667,41 +9655,43 @@
         <v>262</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>146</v>
+        <v>263</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -9749,7 +9739,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>141</v>
+        <v>266</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9770,7 +9760,7 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
@@ -9787,44 +9777,44 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -9872,7 +9862,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9884,25 +9874,25 @@
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>83</v>
+        <v>275</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9910,46 +9900,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>152</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9997,19 +9983,19 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>270</v>
+        <v>154</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -10018,7 +10004,7 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
@@ -10035,44 +10021,44 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -10108,19 +10094,19 @@
         <v>83</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10132,25 +10118,25 @@
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>277</v>
+        <v>155</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10158,10 +10144,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10178,22 +10164,26 @@
         <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -10217,13 +10207,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -10241,7 +10231,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10253,7 +10243,7 @@
         <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -10262,7 +10252,7 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>155</v>
+        <v>287</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10271,7 +10261,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10279,21 +10269,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -10302,21 +10292,23 @@
         <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>160</v>
+        <v>291</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -10340,43 +10332,43 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -10385,7 +10377,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>155</v>
+        <v>287</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10394,7 +10386,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10402,10 +10394,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10422,26 +10414,22 @@
         <v>83</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>284</v>
+        <v>152</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10465,13 +10453,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10489,7 +10477,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>290</v>
+        <v>154</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10501,7 +10489,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -10510,7 +10498,7 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10519,7 +10507,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10527,21 +10515,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -10550,23 +10538,21 @@
         <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>293</v>
+        <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10590,43 +10576,43 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>301</v>
+        <v>163</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -10635,7 +10621,7 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>83</v>
@@ -10644,7 +10630,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10652,10 +10638,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10666,7 +10652,7 @@
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
@@ -10675,19 +10661,23 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>152</v>
+        <v>302</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -10735,19 +10725,19 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>154</v>
+        <v>306</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
@@ -10756,7 +10746,7 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>155</v>
+        <v>307</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>83</v>
@@ -10765,7 +10755,7 @@
         <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>
@@ -10773,21 +10763,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -10799,17 +10789,15 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10846,31 +10834,31 @@
         <v>83</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>83</v>
@@ -10896,14 +10884,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10919,23 +10907,21 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>306</v>
+        <v>159</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>307</v>
+        <v>160</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10971,19 +10957,19 @@
         <v>83</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>310</v>
+        <v>163</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10995,7 +10981,7 @@
         <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>83</v>
@@ -11004,7 +10990,7 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>311</v>
+        <v>155</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>83</v>
@@ -11013,7 +10999,7 @@
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>83</v>
@@ -11021,10 +11007,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11038,25 +11024,29 @@
         <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -11065,7 +11055,7 @@
         <v>83</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>83</v>
@@ -11104,7 +11094,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>154</v>
+        <v>317</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11116,16 +11106,16 @@
         <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>155</v>
+        <v>319</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>83</v>
@@ -11134,7 +11124,7 @@
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>83</v>
@@ -11142,21 +11132,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
@@ -11165,19 +11155,19 @@
         <v>83</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>159</v>
+        <v>322</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11215,31 +11205,31 @@
         <v>83</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -11248,7 +11238,7 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>155</v>
+        <v>326</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>83</v>
@@ -11257,7 +11247,7 @@
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>83</v>
@@ -11265,10 +11255,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11291,19 +11281,17 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11313,7 +11301,7 @@
         <v>83</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>83</v>
@@ -11352,7 +11340,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11367,13 +11355,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>83</v>
@@ -11382,7 +11370,7 @@
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
@@ -11390,10 +11378,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11419,15 +11407,15 @@
         <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -11475,7 +11463,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11484,7 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>83</v>
@@ -11505,7 +11493,7 @@
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11513,10 +11501,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11530,7 +11518,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>83</v>
@@ -11539,17 +11527,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>345</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11559,7 +11549,7 @@
         <v>83</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>83</v>
@@ -11598,7 +11588,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11613,13 +11603,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>83</v>
@@ -11628,7 +11618,7 @@
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>83</v>
@@ -11636,10 +11626,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11665,14 +11655,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11721,7 +11713,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11742,7 +11734,7 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>83</v>
@@ -11751,7 +11743,7 @@
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>83</v>
@@ -11759,10 +11751,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11770,13 +11762,13 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>83</v>
@@ -11785,19 +11777,19 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11807,10 +11799,10 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>83</v>
@@ -11846,7 +11838,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11861,13 +11853,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>83</v>
@@ -11876,7 +11868,7 @@
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>83</v>
@@ -11884,10 +11876,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11895,13 +11887,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>83</v>
@@ -11913,17 +11905,15 @@
         <v>151</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11935,7 +11925,7 @@
         <v>83</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>83</v>
@@ -11971,7 +11961,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11992,7 +11982,7 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>83</v>
@@ -12001,7 +11991,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12009,10 +11999,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12020,13 +12010,13 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>83</v>
@@ -12035,20 +12025,16 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>105</v>
+        <v>381</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -12057,10 +12043,10 @@
         <v>83</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>83</v>
@@ -12096,7 +12082,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12111,13 +12097,13 @@
         <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>83</v>
@@ -12126,7 +12112,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12134,10 +12120,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12145,13 +12131,13 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>83</v>
@@ -12160,16 +12146,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>151</v>
+        <v>388</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12183,7 +12169,7 @@
         <v>83</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>83</v>
@@ -12219,7 +12205,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12240,7 +12226,7 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>
@@ -12249,7 +12235,7 @@
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>83</v>
@@ -12257,10 +12243,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12277,26 +12263,32 @@
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="R78" t="s" s="2">
         <v>83</v>
       </c>
@@ -12340,7 +12332,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12361,16 +12353,16 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>83</v>
@@ -12378,10 +12370,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12389,13 +12381,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>83</v>
@@ -12404,18 +12396,20 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -12463,13 +12457,13 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
@@ -12484,16 +12478,16 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>83</v>
@@ -12501,10 +12495,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12521,32 +12515,26 @@
         <v>83</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>349</v>
+        <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>400</v>
+        <v>152</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q80" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12590,7 +12578,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>399</v>
+        <v>154</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12602,7 +12590,7 @@
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -12611,13 +12599,13 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>405</v>
+        <v>155</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
@@ -12628,46 +12616,44 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>408</v>
+        <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>409</v>
+        <v>159</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>410</v>
+        <v>160</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12703,19 +12689,19 @@
         <v>83</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>407</v>
+        <v>163</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12727,7 +12713,7 @@
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -12736,16 +12722,16 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>413</v>
+        <v>155</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>83</v>
@@ -12753,10 +12739,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12773,22 +12759,26 @@
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12812,13 +12802,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12836,7 +12826,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>154</v>
+        <v>421</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12848,7 +12838,7 @@
         <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>83</v>
@@ -12857,7 +12847,7 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>155</v>
+        <v>422</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
@@ -12866,7 +12856,7 @@
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>83</v>
@@ -12874,21 +12864,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12897,21 +12887,23 @@
         <v>83</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>159</v>
+        <v>425</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>160</v>
+        <v>426</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -12947,31 +12939,31 @@
         <v>83</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>163</v>
+        <v>429</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12980,7 +12972,7 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>155</v>
+        <v>430</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>83</v>
@@ -12989,7 +12981,7 @@
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>83</v>
+        <v>431</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>83</v>
@@ -12997,14 +12989,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>83</v>
+        <v>433</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13014,29 +13006,27 @@
         <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -13060,13 +13050,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -13084,7 +13074,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13093,7 +13083,7 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>103</v>
@@ -13105,7 +13095,7 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
@@ -13114,7 +13104,7 @@
         <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>83</v>
@@ -13122,24 +13112,24 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>83</v>
@@ -13151,17 +13141,15 @@
         <v>151</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -13209,16 +13197,16 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -13230,7 +13218,7 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>83</v>
@@ -13239,7 +13227,7 @@
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>83</v>
@@ -13247,24 +13235,24 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>83</v>
@@ -13276,14 +13264,12 @@
         <v>151</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13332,16 +13318,16 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -13353,7 +13339,7 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>83</v>
@@ -13362,7 +13348,7 @@
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>83</v>
@@ -13370,14 +13356,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13387,7 +13373,7 @@
         <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
@@ -13399,14 +13385,12 @@
         <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13455,7 +13439,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13464,7 +13448,7 @@
         <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>103</v>
@@ -13476,7 +13460,7 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>83</v>
@@ -13485,7 +13469,7 @@
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>83</v>
@@ -13493,10 +13477,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13507,7 +13491,7 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -13519,16 +13503,18 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>151</v>
+        <v>381</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
       </c>
@@ -13576,13 +13562,13 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>83</v>
@@ -13597,7 +13583,7 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>83</v>
@@ -13606,7 +13592,7 @@
         <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>83</v>
@@ -13614,10 +13600,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13640,16 +13626,20 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>151</v>
+        <v>469</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13697,7 +13687,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13718,16 +13708,16 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13735,10 +13725,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13758,21 +13748,19 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>385</v>
+        <v>151</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>466</v>
+        <v>152</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>467</v>
+        <v>153</v>
       </c>
       <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>468</v>
-      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13820,7 +13808,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>469</v>
+        <v>154</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13832,7 +13820,7 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
@@ -13841,7 +13829,7 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>470</v>
+        <v>155</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>83</v>
@@ -13850,7 +13838,7 @@
         <v>83</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>83</v>
@@ -13858,14 +13846,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13881,23 +13869,21 @@
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>474</v>
+        <v>159</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>475</v>
+        <v>160</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13933,19 +13919,19 @@
         <v>83</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>472</v>
+        <v>163</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13957,7 +13943,7 @@
         <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>83</v>
@@ -13966,16 +13952,16 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>478</v>
+        <v>155</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>83</v>
@@ -13983,10 +13969,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13994,28 +13980,28 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>152</v>
+        <v>480</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>153</v>
+        <v>481</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14042,13 +14028,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>83</v>
+        <v>483</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -14066,7 +14052,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>154</v>
+        <v>484</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14075,10 +14061,10 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -14087,7 +14073,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>155</v>
+        <v>486</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14096,7 +14082,7 @@
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14104,44 +14090,46 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>159</v>
+        <v>489</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>160</v>
+        <v>490</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -14177,31 +14165,31 @@
         <v>83</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>163</v>
+        <v>493</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
@@ -14210,7 +14198,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>155</v>
+        <v>494</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14219,7 +14207,7 @@
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>83</v>
+        <v>495</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14227,10 +14215,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14238,7 +14226,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>91</v>
@@ -14247,7 +14235,7 @@
         <v>92</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
@@ -14256,13 +14244,17 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -14288,11 +14280,9 @@
       <c r="X94" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y94" t="s" s="2">
-        <v>486</v>
-      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14310,7 +14300,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14319,7 +14309,7 @@
         <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>103</v>
@@ -14331,7 +14321,7 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>83</v>
@@ -14340,7 +14330,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14348,10 +14338,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14359,13 +14349,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>83</v>
@@ -14374,20 +14364,18 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>151</v>
+        <v>505</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -14435,7 +14423,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14456,7 +14444,7 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>498</v>
+        <v>155</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>83</v>
@@ -14465,7 +14453,7 @@
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>499</v>
+        <v>155</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>83</v>
@@ -14473,10 +14461,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14490,29 +14478,25 @@
         <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -14536,11 +14520,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y96" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z96" t="s" s="2">
-        <v>505</v>
+        <v>83</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14558,7 +14544,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14579,7 +14565,7 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>83</v>
@@ -14588,7 +14574,7 @@
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>507</v>
+        <v>134</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>83</v>
@@ -14596,10 +14582,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14607,13 +14593,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>83</v>
@@ -14622,18 +14608,20 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>509</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -14657,13 +14645,11 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14681,7 +14667,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14696,22 +14682,22 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>155</v>
+        <v>248</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>155</v>
+        <v>522</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14719,10 +14705,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14736,7 +14722,7 @@
         <v>91</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>83</v>
@@ -14745,16 +14731,20 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>385</v>
+        <v>524</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -14802,7 +14792,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14817,33 +14807,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>134</v>
+        <v>532</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>83</v>
+        <v>533</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14851,34 +14841,34 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I99" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>535</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14903,29 +14893,29 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>523</v>
+        <v>83</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>83</v>
+        <v>541</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14940,22 +14930,22 @@
         <v>103</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>248</v>
+        <v>542</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>525</v>
+        <v>155</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14963,12 +14953,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14983,25 +14975,25 @@
         <v>92</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>528</v>
+        <v>345</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15050,7 +15042,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15065,35 +15057,37 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>535</v>
+        <v>155</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>537</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
       </c>
@@ -15105,7 +15099,7 @@
         <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>92</v>
@@ -15114,19 +15108,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O101" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15163,17 +15157,19 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AC101" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15188,13 +15184,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>83</v>
+        <v>550</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>155</v>
@@ -15203,7 +15199,7 @@
         <v>83</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15211,14 +15207,12 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>83</v>
       </c>
@@ -15227,31 +15221,31 @@
         <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>92</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>349</v>
+        <v>552</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15300,13 +15294,13 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>83</v>
@@ -15315,22 +15309,22 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>550</v>
+        <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>155</v>
+        <v>558</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>83</v>
@@ -15338,14 +15332,12 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>83</v>
       </c>
@@ -15357,29 +15349,25 @@
         <v>91</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>553</v>
+        <v>151</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>540</v>
+        <v>152</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
@@ -15427,7 +15415,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>538</v>
+        <v>154</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15439,25 +15427,25 @@
         <v>83</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>554</v>
+        <v>83</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>546</v>
+        <v>155</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>83</v>
@@ -15465,14 +15453,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -15482,29 +15470,27 @@
         <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>556</v>
+        <v>136</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>557</v>
+        <v>159</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>558</v>
+        <v>160</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>83</v>
       </c>
@@ -15540,19 +15526,19 @@
         <v>83</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>555</v>
+        <v>163</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15564,7 +15550,7 @@
         <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>83</v>
@@ -15573,16 +15559,16 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>561</v>
+        <v>155</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>562</v>
+        <v>83</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>563</v>
+        <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>83</v>
@@ -15590,10 +15576,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15610,22 +15596,26 @@
         <v>83</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>152</v>
+        <v>563</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
       </c>
@@ -15637,7 +15627,7 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>83</v>
@@ -15649,13 +15639,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15673,7 +15663,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>154</v>
+        <v>570</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15685,7 +15675,7 @@
         <v>83</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>83</v>
@@ -15694,7 +15684,7 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>155</v>
+        <v>422</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>83</v>
@@ -15703,7 +15693,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>83</v>
+        <v>571</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15711,21 +15701,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>83</v>
@@ -15734,19 +15724,19 @@
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>159</v>
+        <v>573</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>160</v>
+        <v>574</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>161</v>
+        <v>575</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15760,7 +15750,7 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>83</v>
@@ -15772,43 +15762,43 @@
         <v>83</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>163</v>
+        <v>579</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>83</v>
@@ -15817,7 +15807,7 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>155</v>
+        <v>422</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>83</v>
@@ -15826,7 +15816,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15834,10 +15824,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15854,25 +15844,25 @@
         <v>83</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>570</v>
+        <v>428</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15885,7 +15875,7 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>83</v>
@@ -15897,13 +15887,13 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>572</v>
+        <v>83</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>573</v>
+        <v>83</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
@@ -15921,7 +15911,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15942,7 +15932,7 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>83</v>
@@ -15951,7 +15941,7 @@
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15959,10 +15949,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15973,10 +15963,10 @@
         <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>83</v>
@@ -15985,17 +15975,15 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -16008,7 +15996,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -16020,13 +16008,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>581</v>
+        <v>83</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>582</v>
+        <v>83</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -16044,13 +16032,13 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>83</v>
@@ -16065,7 +16053,7 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>426</v>
+        <v>593</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16074,7 +16062,7 @@
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16082,14 +16070,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>83</v>
+        <v>596</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16099,7 +16087,7 @@
         <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>83</v>
@@ -16111,17 +16099,13 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -16133,7 +16117,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -16169,7 +16153,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16190,7 +16174,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>434</v>
+        <v>601</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>83</v>
@@ -16199,7 +16183,7 @@
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16207,24 +16191,24 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>83</v>
@@ -16236,12 +16220,14 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -16254,7 +16240,7 @@
         <v>83</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>83</v>
@@ -16290,13 +16276,13 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
@@ -16311,7 +16297,7 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16320,7 +16306,7 @@
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16328,14 +16314,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16357,10 +16343,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16375,7 +16361,7 @@
         <v>83</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>603</v>
+        <v>83</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>83</v>
@@ -16387,13 +16373,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>83</v>
+        <v>616</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>617</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16411,7 +16397,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16432,7 +16418,7 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>83</v>
@@ -16441,7 +16427,7 @@
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16449,14 +16435,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16466,7 +16452,7 @@
         <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>83</v>
@@ -16478,14 +16464,12 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>611</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -16498,7 +16482,7 @@
         <v>83</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>83</v>
@@ -16534,7 +16518,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16555,7 +16539,7 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>83</v>
@@ -16564,7 +16548,7 @@
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16572,14 +16556,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>617</v>
+        <v>83</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16589,7 +16573,7 @@
         <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>83</v>
@@ -16601,12 +16585,14 @@
         <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16631,13 +16617,13 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>620</v>
+        <v>83</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>621</v>
+        <v>83</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -16655,7 +16641,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16676,7 +16662,7 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
@@ -16685,7 +16671,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16693,14 +16679,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>626</v>
+        <v>83</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16719,16 +16705,18 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>151</v>
+        <v>381</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
@@ -16740,7 +16728,7 @@
         <v>83</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>83</v>
@@ -16776,7 +16764,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16797,7 +16785,7 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>631</v>
+        <v>466</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>83</v>
@@ -16806,7 +16794,7 @@
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16814,10 +16802,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16837,21 +16825,21 @@
         <v>83</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>151</v>
+        <v>289</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -16875,13 +16863,13 @@
         <v>83</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>83</v>
+        <v>647</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>83</v>
+        <v>648</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16899,7 +16887,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16920,16 +16908,16 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>83</v>
+        <v>650</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16937,10 +16925,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16954,26 +16942,28 @@
         <v>91</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>385</v>
+        <v>653</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="O116" t="s" s="2">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16986,7 +16976,7 @@
         <v>83</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>644</v>
+        <v>83</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>83</v>
@@ -17022,7 +17012,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17043,16 +17033,16 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>470</v>
+        <v>658</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17060,10 +17050,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17074,7 +17064,7 @@
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
@@ -17086,17 +17076,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>293</v>
+        <v>661</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="O117" t="s" s="2">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17121,13 +17113,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>651</v>
+        <v>83</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>652</v>
+        <v>83</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -17145,13 +17137,13 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
@@ -17166,16 +17158,16 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>654</v>
+        <v>155</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>83</v>
@@ -17183,10 +17175,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17197,7 +17189,7 @@
         <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>83</v>
@@ -17209,19 +17201,19 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17270,19 +17262,19 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>674</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
@@ -17291,7 +17283,7 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>155</v>
@@ -17300,7 +17292,7 @@
         <v>83</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>663</v>
+        <v>83</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>83</v>
@@ -17308,10 +17300,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17322,7 +17314,7 @@
         <v>81</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>83</v>
@@ -17334,20 +17326,16 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>665</v>
+        <v>151</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>666</v>
+        <v>152</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>669</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -17395,19 +17383,19 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>664</v>
+        <v>154</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>83</v>
@@ -17416,16 +17404,16 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>670</v>
+        <v>155</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>671</v>
+        <v>83</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>83</v>
@@ -17433,14 +17421,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17459,20 +17447,18 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>673</v>
+        <v>136</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>674</v>
+        <v>159</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>675</v>
+        <v>160</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>677</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -17520,7 +17506,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>672</v>
+        <v>163</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17532,7 +17518,7 @@
         <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>678</v>
+        <v>142</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>83</v>
@@ -17541,10 +17527,10 @@
         <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>679</v>
+        <v>155</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17558,42 +17544,46 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>83</v>
+        <v>679</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>152</v>
+        <v>680</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -17641,19 +17631,19 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>154</v>
+        <v>682</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>83</v>
@@ -17662,7 +17652,7 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>83</v>
@@ -17679,14 +17669,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -17705,18 +17695,18 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>159</v>
+        <v>684</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>685</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>686</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
@@ -17740,13 +17730,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>83</v>
+        <v>687</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>83</v>
+        <v>688</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17764,7 +17754,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>163</v>
+        <v>683</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17776,7 +17766,7 @@
         <v>83</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>83</v>
@@ -17785,16 +17775,16 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN122" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>83</v>
+        <v>690</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17802,45 +17792,43 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>683</v>
+        <v>83</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>269</v>
+        <v>694</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17889,19 +17877,19 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>83</v>
@@ -17910,16 +17898,16 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>134</v>
+        <v>409</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>83</v>
+        <v>695</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17927,10 +17915,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17953,17 +17941,19 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>699</v>
+      </c>
       <c r="O124" t="s" s="2">
-        <v>690</v>
+        <v>473</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17988,13 +17978,13 @@
         <v>83</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>691</v>
+        <v>83</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>692</v>
+        <v>83</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>83</v>
@@ -18012,7 +18002,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18033,7 +18023,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>693</v>
+        <v>474</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18042,7 +18032,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18050,10 +18040,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18076,17 +18066,17 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>408</v>
+        <v>552</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18135,7 +18125,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18156,7 +18146,7 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>413</v>
+        <v>557</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>155</v>
@@ -18165,7 +18155,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18173,10 +18163,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18187,7 +18177,7 @@
         <v>81</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>83</v>
@@ -18199,19 +18189,17 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>473</v>
+        <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>701</v>
+        <v>515</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>703</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>477</v>
+        <v>708</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18236,13 +18224,13 @@
         <v>83</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>83</v>
+        <v>709</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>83</v>
+        <v>710</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -18260,13 +18248,13 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>83</v>
@@ -18281,7 +18269,7 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>478</v>
+        <v>248</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>155</v>
@@ -18290,7 +18278,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18298,10 +18286,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18324,17 +18312,17 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18383,7 +18371,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18392,7 +18380,7 @@
         <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>83</v>
+        <v>716</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>103</v>
@@ -18404,7 +18392,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>561</v>
+        <v>717</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18413,7 +18401,7 @@
         <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18421,10 +18409,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18447,18 +18435,16 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>519</v>
+        <v>720</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>712</v>
-      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
@@ -18482,13 +18468,13 @@
         <v>83</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>713</v>
+        <v>83</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>714</v>
+        <v>83</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>83</v>
@@ -18506,7 +18492,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18527,7 +18513,7 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>248</v>
+        <v>722</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>155</v>
@@ -18536,7 +18522,7 @@
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>715</v>
+        <v>83</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>83</v>
@@ -18544,10 +18530,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18558,7 +18544,7 @@
         <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>83</v>
@@ -18570,17 +18556,19 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>392</v>
+        <v>669</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>726</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18629,16 +18617,16 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>720</v>
+        <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>103</v>
@@ -18650,16 +18638,16 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>155</v>
+        <v>729</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>722</v>
+        <v>83</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>83</v>
@@ -18667,10 +18655,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18693,13 +18681,13 @@
         <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>385</v>
+        <v>151</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>724</v>
+        <v>152</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>725</v>
+        <v>153</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18750,7 +18738,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>723</v>
+        <v>154</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18762,7 +18750,7 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>83</v>
@@ -18771,10 +18759,10 @@
         <v>83</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>726</v>
+        <v>155</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
@@ -18788,14 +18776,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18814,20 +18802,18 @@
         <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>673</v>
+        <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>728</v>
+        <v>159</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>729</v>
+        <v>160</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>731</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>83</v>
       </c>
@@ -18875,7 +18861,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>727</v>
+        <v>163</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18887,7 +18873,7 @@
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>83</v>
@@ -18896,10 +18882,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>732</v>
+        <v>155</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>733</v>
+        <v>83</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
@@ -18913,42 +18899,46 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>83</v>
+        <v>679</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>152</v>
+        <v>680</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
       </c>
@@ -18996,19 +18986,19 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>154</v>
+        <v>682</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>83</v>
@@ -19017,7 +19007,7 @@
         <v>83</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>83</v>
@@ -19034,24 +19024,24 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>83</v>
@@ -19060,18 +19050,20 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>159</v>
+        <v>734</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>160</v>
+        <v>735</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>737</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
       </c>
@@ -19095,13 +19087,11 @@
         <v>83</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>83</v>
+        <v>738</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19119,19 +19109,19 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>163</v>
+        <v>733</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>83</v>
@@ -19140,16 +19130,16 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>155</v>
+        <v>739</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>83</v>
+        <v>740</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>83</v>
+        <v>741</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19157,45 +19147,45 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>683</v>
+        <v>83</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>136</v>
+        <v>345</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>684</v>
+        <v>743</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>685</v>
+        <v>744</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>161</v>
+        <v>745</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>269</v>
+        <v>746</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -19244,19 +19234,19 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>686</v>
+        <v>742</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>83</v>
@@ -19265,16 +19255,16 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>134</v>
+        <v>747</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>83</v>
+        <v>748</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>83</v>
+        <v>749</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19282,24 +19272,24 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>83</v>
+        <v>751</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>83</v>
@@ -19308,20 +19298,18 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>293</v>
+        <v>752</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>741</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>83</v>
       </c>
@@ -19345,11 +19333,13 @@
         <v>83</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Y135" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z135" t="s" s="2">
-        <v>742</v>
+        <v>83</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>83</v>
@@ -19367,13 +19357,13 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>83</v>
@@ -19388,16 +19378,16 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>744</v>
+        <v>155</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>83</v>
@@ -19405,10 +19395,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19428,22 +19418,22 @@
         <v>83</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19492,7 +19482,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19513,16 +19503,16 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>751</v>
+        <v>717</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>753</v>
+        <v>83</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>83</v>
@@ -19530,14 +19520,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>755</v>
+        <v>83</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -19550,24 +19540,26 @@
         <v>83</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>756</v>
+        <v>669</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>767</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>768</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
       </c>
@@ -19615,7 +19607,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19636,7 +19628,7 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>155</v>
@@ -19645,7 +19637,7 @@
         <v>83</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>761</v>
+        <v>83</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>83</v>
@@ -19653,10 +19645,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19676,23 +19668,19 @@
         <v>83</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>392</v>
+        <v>151</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>763</v>
+        <v>152</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>766</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>83</v>
       </c>
@@ -19740,7 +19728,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>762</v>
+        <v>154</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19752,7 +19740,7 @@
         <v>83</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>83</v>
@@ -19761,10 +19749,10 @@
         <v>83</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>721</v>
+        <v>155</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>767</v>
+        <v>83</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>83</v>
@@ -19778,14 +19766,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19798,26 +19786,24 @@
         <v>83</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>673</v>
+        <v>136</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>769</v>
+        <v>159</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>770</v>
+        <v>160</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>772</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>83</v>
       </c>
@@ -19865,7 +19851,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>768</v>
+        <v>163</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19877,7 +19863,7 @@
         <v>83</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>83</v>
@@ -19886,10 +19872,10 @@
         <v>83</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>773</v>
+        <v>155</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
@@ -19903,42 +19889,46 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>83</v>
+        <v>679</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>152</v>
+        <v>680</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
       </c>
@@ -19986,19 +19976,19 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>154</v>
+        <v>682</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>83</v>
@@ -20007,7 +19997,7 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>83</v>
@@ -20024,21 +20014,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>83</v>
@@ -20047,19 +20037,19 @@
         <v>83</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>136</v>
+        <v>774</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>159</v>
+        <v>775</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>160</v>
+        <v>776</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>161</v>
+        <v>777</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20109,19 +20099,19 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>163</v>
+        <v>773</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>83</v>
@@ -20130,16 +20120,16 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN141" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>83</v>
+        <v>778</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>83</v>
@@ -20147,46 +20137,42 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>683</v>
+        <v>83</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>684</v>
+        <v>780</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>83</v>
       </c>
@@ -20210,13 +20196,13 @@
         <v>83</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>83</v>
+        <v>781</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>83</v>
+        <v>782</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>83</v>
@@ -20234,19 +20220,19 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>686</v>
+        <v>779</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>83</v>
@@ -20255,10 +20241,10 @@
         <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>134</v>
+        <v>783</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>83</v>
@@ -20267,255 +20253,11 @@
         <v>83</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AQ143" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
-      <c r="P144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ144" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ144">
+  <autoFilter ref="A1:AQ142">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20525,7 +20267,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI141">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="785">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1283,6 +1283,9 @@
   </si>
   <si>
     <t>Need to be able to track the patient by multiple names. Examples are your official name and a partner name.</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>name</t>
@@ -12472,22 +12475,22 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>83</v>
@@ -12495,10 +12498,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12616,10 +12619,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12739,10 +12742,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12768,16 +12771,16 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12805,10 +12808,10 @@
         <v>183</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12826,7 +12829,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12847,7 +12850,7 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
@@ -12856,7 +12859,7 @@
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>83</v>
@@ -12864,10 +12867,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12893,16 +12896,16 @@
         <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12951,7 +12954,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12972,7 +12975,7 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>83</v>
@@ -12981,7 +12984,7 @@
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>83</v>
@@ -12989,14 +12992,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13018,13 +13021,13 @@
         <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13074,7 +13077,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13083,7 +13086,7 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>103</v>
@@ -13095,7 +13098,7 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
@@ -13104,7 +13107,7 @@
         <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>83</v>
@@ -13112,14 +13115,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13141,13 +13144,13 @@
         <v>151</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13197,7 +13200,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13206,7 +13209,7 @@
         <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -13218,7 +13221,7 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>83</v>
@@ -13227,7 +13230,7 @@
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>83</v>
@@ -13235,10 +13238,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13264,10 +13267,10 @@
         <v>151</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13318,7 +13321,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13339,7 +13342,7 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>83</v>
@@ -13348,7 +13351,7 @@
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>83</v>
@@ -13356,10 +13359,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13385,10 +13388,10 @@
         <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13439,7 +13442,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13460,7 +13463,7 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>83</v>
@@ -13469,7 +13472,7 @@
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>83</v>
@@ -13477,10 +13480,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13506,14 +13509,14 @@
         <v>381</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13562,7 +13565,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13583,7 +13586,7 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>83</v>
@@ -13592,7 +13595,7 @@
         <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>83</v>
@@ -13600,10 +13603,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13626,19 +13629,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13687,7 +13690,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13702,22 +13705,22 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13725,10 +13728,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13846,10 +13849,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13969,10 +13972,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13998,10 +14001,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14031,10 +14034,10 @@
         <v>183</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -14052,7 +14055,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14061,7 +14064,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14073,7 +14076,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14082,7 +14085,7 @@
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14090,10 +14093,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14119,16 +14122,16 @@
         <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14177,7 +14180,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14198,7 +14201,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14207,7 +14210,7 @@
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14215,10 +14218,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14244,16 +14247,16 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14282,7 +14285,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14300,7 +14303,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14321,7 +14324,7 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>83</v>
@@ -14330,7 +14333,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14338,10 +14341,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14364,16 +14367,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14423,7 +14426,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14461,10 +14464,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14490,10 +14493,10 @@
         <v>381</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14544,7 +14547,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14565,7 +14568,7 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>83</v>
@@ -14582,10 +14585,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14611,16 +14614,16 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14649,7 +14652,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14667,7 +14670,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14682,7 +14685,7 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
@@ -14691,13 +14694,13 @@
         <v>248</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14705,10 +14708,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14731,19 +14734,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14792,7 +14795,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14807,33 +14810,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14856,19 +14859,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14905,17 +14908,17 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14936,7 +14939,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>155</v>
@@ -14945,7 +14948,7 @@
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14953,13 +14956,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -14984,16 +14987,16 @@
         <v>345</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15042,7 +15045,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15057,13 +15060,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>155</v>
@@ -15072,7 +15075,7 @@
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>83</v>
@@ -15080,13 +15083,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -15108,19 +15111,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15169,7 +15172,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15184,13 +15187,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>155</v>
@@ -15199,7 +15202,7 @@
         <v>83</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15207,10 +15210,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15233,19 +15236,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15294,7 +15297,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15309,22 +15312,22 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>83</v>
@@ -15332,10 +15335,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15453,10 +15456,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15576,10 +15579,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15605,16 +15608,16 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15627,7 +15630,7 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>83</v>
@@ -15642,10 +15645,10 @@
         <v>183</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15663,7 +15666,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15684,7 +15687,7 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>83</v>
@@ -15693,7 +15696,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15701,10 +15704,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15730,13 +15733,13 @@
         <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15750,7 +15753,7 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>83</v>
@@ -15765,10 +15768,10 @@
         <v>183</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -15786,7 +15789,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15807,7 +15810,7 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>83</v>
@@ -15816,7 +15819,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15824,10 +15827,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15853,16 +15856,16 @@
         <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15875,7 +15878,7 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>83</v>
@@ -15911,7 +15914,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15932,7 +15935,7 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>83</v>
@@ -15941,7 +15944,7 @@
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15949,10 +15952,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15978,10 +15981,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15996,7 +15999,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -16032,7 +16035,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16053,7 +16056,7 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16062,7 +16065,7 @@
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16070,14 +16073,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16099,10 +16102,10 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16117,7 +16120,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -16153,7 +16156,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16174,7 +16177,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>83</v>
@@ -16183,7 +16186,7 @@
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16191,14 +16194,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16220,13 +16223,13 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16240,7 +16243,7 @@
         <v>83</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>83</v>
@@ -16276,7 +16279,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16297,7 +16300,7 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16306,7 +16309,7 @@
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16314,14 +16317,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16343,10 +16346,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16376,10 +16379,10 @@
         <v>294</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16397,7 +16400,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16418,7 +16421,7 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>83</v>
@@ -16427,7 +16430,7 @@
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16435,14 +16438,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16464,10 +16467,10 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16482,7 +16485,7 @@
         <v>83</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>83</v>
@@ -16518,7 +16521,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16539,7 +16542,7 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>83</v>
@@ -16548,7 +16551,7 @@
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16556,10 +16559,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16585,13 +16588,13 @@
         <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16641,7 +16644,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16662,7 +16665,7 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
@@ -16671,7 +16674,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16679,10 +16682,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16708,14 +16711,14 @@
         <v>381</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16728,7 +16731,7 @@
         <v>83</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>83</v>
@@ -16764,7 +16767,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16785,7 +16788,7 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>83</v>
@@ -16794,7 +16797,7 @@
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16802,10 +16805,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16831,14 +16834,14 @@
         <v>289</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16866,10 +16869,10 @@
         <v>294</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16887,7 +16890,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16908,16 +16911,16 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16925,10 +16928,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16951,19 +16954,19 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -17012,7 +17015,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17033,7 +17036,7 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>155</v>
@@ -17042,7 +17045,7 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17050,10 +17053,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17076,19 +17079,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17137,7 +17140,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17158,7 +17161,7 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>155</v>
@@ -17167,7 +17170,7 @@
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>83</v>
@@ -17175,10 +17178,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17201,19 +17204,19 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17262,7 +17265,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17274,7 +17277,7 @@
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
@@ -17283,7 +17286,7 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>155</v>
@@ -17300,10 +17303,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17421,10 +17424,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17544,14 +17547,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17573,10 +17576,10 @@
         <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>161</v>
@@ -17631,7 +17634,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17669,10 +17672,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17698,14 +17701,14 @@
         <v>289</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17733,10 +17736,10 @@
         <v>294</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17754,7 +17757,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17775,7 +17778,7 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>155</v>
@@ -17784,7 +17787,7 @@
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17792,10 +17795,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17821,14 +17824,14 @@
         <v>404</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17877,7 +17880,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17898,7 +17901,7 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>155</v>
@@ -17907,7 +17910,7 @@
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17915,10 +17918,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17941,19 +17944,19 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18002,7 +18005,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18023,7 +18026,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18032,7 +18035,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18040,10 +18043,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18066,17 +18069,17 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18125,7 +18128,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18146,7 +18149,7 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>155</v>
@@ -18155,7 +18158,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18163,10 +18166,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18192,14 +18195,14 @@
         <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18227,10 +18230,10 @@
         <v>183</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -18248,7 +18251,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18278,7 +18281,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18286,10 +18289,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18315,14 +18318,14 @@
         <v>388</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18371,7 +18374,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18380,7 +18383,7 @@
         <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>103</v>
@@ -18392,7 +18395,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18401,7 +18404,7 @@
         <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18409,10 +18412,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18438,10 +18441,10 @@
         <v>381</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18492,7 +18495,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18513,7 +18516,7 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>155</v>
@@ -18530,10 +18533,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18556,19 +18559,19 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18617,7 +18620,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18638,10 +18641,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18655,10 +18658,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18776,10 +18779,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18899,14 +18902,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18928,10 +18931,10 @@
         <v>136</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>161</v>
@@ -18986,7 +18989,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19024,10 +19027,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19053,16 +19056,16 @@
         <v>289</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19091,7 +19094,7 @@
       </c>
       <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19109,7 +19112,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>91</v>
@@ -19124,22 +19127,22 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19147,10 +19150,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19176,16 +19179,16 @@
         <v>345</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -19234,7 +19237,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19255,16 +19258,16 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19272,14 +19275,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19298,16 +19301,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19357,7 +19360,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19378,7 +19381,7 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>155</v>
@@ -19387,7 +19390,7 @@
         <v>83</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>83</v>
@@ -19395,10 +19398,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19424,16 +19427,16 @@
         <v>388</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19482,7 +19485,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19503,10 +19506,10 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>83</v>
@@ -19520,10 +19523,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19546,19 +19549,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -19607,7 +19610,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19628,7 +19631,7 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>155</v>
@@ -19645,10 +19648,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19766,10 +19769,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19889,14 +19892,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19918,10 +19921,10 @@
         <v>136</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>161</v>
@@ -19976,7 +19979,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20014,10 +20017,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20040,16 +20043,16 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20099,7 +20102,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -20129,7 +20132,7 @@
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>83</v>
@@ -20137,10 +20140,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20166,10 +20169,10 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20199,10 +20202,10 @@
         <v>183</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>83</v>
@@ -20220,7 +20223,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>91</v>
@@ -20241,7 +20244,7 @@
         <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>155</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="788">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1285,7 +1285,7 @@
     <t>Need to be able to track the patient by multiple names. Examples are your official name and a partner name.</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2022: target not supported</t>
   </si>
   <si>
     <t>name</t>
@@ -1487,6 +1487,9 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
+    <t>2023: target not supported</t>
+  </si>
+  <si>
     <t>telecom</t>
   </si>
   <si>
@@ -1741,6 +1744,9 @@
   </si>
   <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
+  </si>
+  <si>
+    <t>2024: target not supported</t>
   </si>
   <si>
     <t>addr</t>
@@ -2304,6 +2310,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/simple-language</t>
+  </si>
+  <si>
+    <t>2025: target not supported</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -13705,22 +13714,22 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>409</v>
+        <v>475</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13728,10 +13737,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13849,10 +13858,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13972,10 +13981,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14001,10 +14010,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14034,10 +14043,10 @@
         <v>183</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -14055,7 +14064,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14064,7 +14073,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14076,7 +14085,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14085,7 +14094,7 @@
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14093,10 +14102,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14122,16 +14131,16 @@
         <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14180,7 +14189,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14201,7 +14210,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14210,7 +14219,7 @@
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14218,10 +14227,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14247,16 +14256,16 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14285,7 +14294,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14303,7 +14312,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14333,7 +14342,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14341,10 +14350,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14367,16 +14376,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14426,7 +14435,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14464,10 +14473,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14493,10 +14502,10 @@
         <v>381</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14547,7 +14556,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14585,10 +14594,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14614,16 +14623,16 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14652,7 +14661,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14670,7 +14679,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14685,7 +14694,7 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
@@ -14694,13 +14703,13 @@
         <v>248</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14708,10 +14717,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14734,19 +14743,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14795,7 +14804,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14810,33 +14819,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14859,19 +14868,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14908,17 +14917,17 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14939,7 +14948,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>155</v>
@@ -14948,7 +14957,7 @@
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14956,13 +14965,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -14987,16 +14996,16 @@
         <v>345</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15045,7 +15054,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15060,13 +15069,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>155</v>
@@ -15075,7 +15084,7 @@
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>83</v>
@@ -15083,13 +15092,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -15111,19 +15120,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15172,7 +15181,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15187,13 +15196,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>155</v>
@@ -15202,7 +15211,7 @@
         <v>83</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15210,10 +15219,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15236,19 +15245,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15297,7 +15306,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15312,22 +15321,22 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>409</v>
+        <v>559</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>83</v>
@@ -15335,10 +15344,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15456,10 +15465,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15579,10 +15588,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15608,16 +15617,16 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15630,7 +15639,7 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>83</v>
@@ -15645,10 +15654,10 @@
         <v>183</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15666,7 +15675,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15696,7 +15705,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15704,10 +15713,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15733,13 +15742,13 @@
         <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15753,7 +15762,7 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>83</v>
@@ -15768,10 +15777,10 @@
         <v>183</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -15789,7 +15798,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15819,7 +15828,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15827,10 +15836,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15856,13 +15865,13 @@
         <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>429</v>
@@ -15878,7 +15887,7 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>83</v>
@@ -15914,7 +15923,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15944,7 +15953,7 @@
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15952,10 +15961,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15981,10 +15990,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15999,7 +16008,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -16035,7 +16044,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16056,7 +16065,7 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16065,7 +16074,7 @@
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16073,14 +16082,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16102,10 +16111,10 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16120,7 +16129,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -16156,7 +16165,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16177,7 +16186,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>83</v>
@@ -16186,7 +16195,7 @@
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16194,14 +16203,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16223,13 +16232,13 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16243,7 +16252,7 @@
         <v>83</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>83</v>
@@ -16279,7 +16288,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16300,7 +16309,7 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16309,7 +16318,7 @@
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16317,14 +16326,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16346,10 +16355,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16379,10 +16388,10 @@
         <v>294</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16400,7 +16409,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16421,7 +16430,7 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>83</v>
@@ -16430,7 +16439,7 @@
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16438,14 +16447,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16467,10 +16476,10 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16485,7 +16494,7 @@
         <v>83</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>83</v>
@@ -16521,7 +16530,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16542,7 +16551,7 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>83</v>
@@ -16551,7 +16560,7 @@
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16559,10 +16568,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16588,13 +16597,13 @@
         <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16644,7 +16653,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16665,7 +16674,7 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
@@ -16674,7 +16683,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16682,10 +16691,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16711,14 +16720,14 @@
         <v>381</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16731,7 +16740,7 @@
         <v>83</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>83</v>
@@ -16767,7 +16776,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16797,7 +16806,7 @@
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16805,10 +16814,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16834,14 +16843,14 @@
         <v>289</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16869,10 +16878,10 @@
         <v>294</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16890,7 +16899,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16911,16 +16920,16 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16928,10 +16937,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16954,19 +16963,19 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -17015,7 +17024,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17036,7 +17045,7 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>155</v>
@@ -17045,7 +17054,7 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17053,10 +17062,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17079,19 +17088,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17140,7 +17149,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17161,7 +17170,7 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>155</v>
@@ -17170,7 +17179,7 @@
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>83</v>
@@ -17178,10 +17187,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17204,19 +17213,19 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17265,7 +17274,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17277,7 +17286,7 @@
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
@@ -17286,7 +17295,7 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>155</v>
@@ -17303,10 +17312,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17424,10 +17433,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17547,14 +17556,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17576,10 +17585,10 @@
         <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>161</v>
@@ -17634,7 +17643,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17672,10 +17681,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17701,14 +17710,14 @@
         <v>289</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17736,10 +17745,10 @@
         <v>294</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17757,7 +17766,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17778,7 +17787,7 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>155</v>
@@ -17787,7 +17796,7 @@
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17795,10 +17804,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17824,14 +17833,14 @@
         <v>404</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17880,7 +17889,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17910,7 +17919,7 @@
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17918,10 +17927,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17947,13 +17956,13 @@
         <v>470</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>474</v>
@@ -18005,7 +18014,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18026,7 +18035,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18035,7 +18044,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18043,10 +18052,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18069,17 +18078,17 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18128,7 +18137,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18149,7 +18158,7 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>155</v>
@@ -18158,7 +18167,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18166,10 +18175,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18195,14 +18204,14 @@
         <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18230,10 +18239,10 @@
         <v>183</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -18251,7 +18260,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18281,7 +18290,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18289,10 +18298,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18318,14 +18327,14 @@
         <v>388</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18374,7 +18383,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18383,7 +18392,7 @@
         <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>103</v>
@@ -18395,7 +18404,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18404,7 +18413,7 @@
         <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18412,10 +18421,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18441,10 +18450,10 @@
         <v>381</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18495,7 +18504,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18516,7 +18525,7 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>155</v>
@@ -18533,10 +18542,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18559,19 +18568,19 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18620,7 +18629,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18641,10 +18650,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18658,10 +18667,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18779,10 +18788,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18902,14 +18911,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18931,10 +18940,10 @@
         <v>136</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>161</v>
@@ -18989,7 +18998,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19027,10 +19036,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19056,16 +19065,16 @@
         <v>289</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19094,7 +19103,7 @@
       </c>
       <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19112,7 +19121,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>91</v>
@@ -19127,22 +19136,22 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>409</v>
+        <v>742</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19150,10 +19159,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19179,16 +19188,16 @@
         <v>345</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -19237,7 +19246,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19258,16 +19267,16 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19275,14 +19284,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19301,16 +19310,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19360,7 +19369,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19381,7 +19390,7 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>155</v>
@@ -19390,7 +19399,7 @@
         <v>83</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>83</v>
@@ -19398,10 +19407,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19427,16 +19436,16 @@
         <v>388</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19485,7 +19494,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19506,10 +19515,10 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>83</v>
@@ -19523,10 +19532,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19549,19 +19558,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -19610,7 +19619,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19631,7 +19640,7 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>155</v>
@@ -19648,10 +19657,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19769,10 +19778,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19892,14 +19901,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19921,10 +19930,10 @@
         <v>136</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>161</v>
@@ -19979,7 +19988,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20017,10 +20026,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20043,16 +20052,16 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20102,7 +20111,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -20132,7 +20141,7 @@
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>83</v>
@@ -20140,10 +20149,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20169,10 +20178,10 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20202,28 +20211,28 @@
         <v>183</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="Z142" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF142" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>91</v>
@@ -20244,7 +20253,7 @@
         <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>155</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5567" uniqueCount="791">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,6 +543,10 @@
     <t>5</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}VAERSPatient-1948:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
+  </si>
+  <si>
     <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native case not xsi:nil</t>
   </si>
   <si>
@@ -604,7 +608,11 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 Other Race case not xsi:nil</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VAERSPatient-1949:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}VAERSPatient-1950:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}VAERSPatient-1951:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}VAERSPatient-1952:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}VAERSPatient-1953:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}VAERSPatient-1954:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
+  </si>
+  <si>
+    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:detailed</t>
@@ -717,7 +725,11 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category</t>
   </si>
   <si>
-    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH other case not xsi:nil</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VAERSPatient-1955:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}VAERSPatient-1956:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}VAERSPatient-1957:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}VAERSPatient-1958:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
+  </si>
+  <si>
+    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" case not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:detailed</t>
@@ -4393,10 +4405,10 @@
         <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
@@ -4419,10 +4431,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4540,10 +4552,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4661,10 +4673,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4690,13 +4702,13 @@
         <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4746,7 +4758,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4784,10 +4796,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4810,13 +4822,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4843,13 +4855,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4867,7 +4879,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4879,10 +4891,10 @@
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
@@ -4905,13 +4917,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>83</v>
@@ -4936,10 +4948,10 @@
         <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -5028,10 +5040,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5149,10 +5161,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5272,10 +5284,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5301,13 +5313,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5315,7 +5327,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -5357,7 +5369,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -5395,10 +5407,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5421,13 +5433,13 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5454,11 +5466,11 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -5476,7 +5488,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5514,13 +5526,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>83</v>
@@ -5545,10 +5557,10 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5637,10 +5649,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5758,10 +5770,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5881,10 +5893,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5910,13 +5922,13 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5924,7 +5936,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5966,7 +5978,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -6004,10 +6016,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6033,10 +6045,10 @@
         <v>151</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6087,7 +6099,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -6125,10 +6137,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6154,13 +6166,13 @@
         <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6168,7 +6180,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>83</v>
@@ -6210,7 +6222,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -6248,10 +6260,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6274,13 +6286,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6331,7 +6343,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6369,13 +6381,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>83</v>
@@ -6397,13 +6409,13 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6492,7 +6504,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>150</v>
@@ -6613,7 +6625,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>157</v>
@@ -6736,7 +6748,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>157</v>
@@ -6859,10 +6871,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6980,10 +6992,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7101,10 +7113,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7130,13 +7142,13 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7186,7 +7198,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>91</v>
@@ -7224,10 +7236,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7250,13 +7262,13 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7283,11 +7295,11 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7305,7 +7317,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7317,10 +7329,10 @@
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>226</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
@@ -7343,13 +7355,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>83</v>
@@ -7374,10 +7386,10 @@
         <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7466,10 +7478,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7587,10 +7599,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7710,10 +7722,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7739,13 +7751,13 @@
         <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7753,7 +7765,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>83</v>
@@ -7795,7 +7807,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7833,10 +7845,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7859,13 +7871,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7892,11 +7904,11 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7914,7 +7926,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7952,13 +7964,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -7983,10 +7995,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8075,10 +8087,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8196,10 +8208,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8319,10 +8331,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8348,13 +8360,13 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8362,7 +8374,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -8404,7 +8416,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -8442,10 +8454,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8471,10 +8483,10 @@
         <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8525,7 +8537,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8563,10 +8575,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8592,13 +8604,13 @@
         <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8606,7 +8618,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8648,7 +8660,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8686,10 +8698,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8712,13 +8724,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8769,7 +8781,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8807,13 +8819,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>83</v>
@@ -8835,16 +8847,16 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8915,7 +8927,7 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
@@ -8932,13 +8944,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>83</v>
@@ -8960,7 +8972,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>137</v>
@@ -9055,13 +9067,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>83</v>
@@ -9083,13 +9095,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9178,7 +9190,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>150</v>
@@ -9299,7 +9311,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>157</v>
@@ -9420,10 +9432,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9449,13 +9461,13 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9463,7 +9475,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>83</v>
@@ -9505,7 +9517,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -9543,10 +9555,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9572,10 +9584,10 @@
         <v>151</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9626,7 +9638,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9641,7 +9653,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
@@ -9664,10 +9676,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9693,16 +9705,16 @@
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9751,7 +9763,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9789,10 +9801,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9815,17 +9827,17 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9874,7 +9886,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9889,22 +9901,22 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9912,10 +9924,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10033,10 +10045,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10156,10 +10168,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10185,16 +10197,16 @@
         <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10219,13 +10231,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -10243,7 +10255,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10264,7 +10276,7 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10281,10 +10293,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10307,19 +10319,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10344,13 +10356,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -10368,7 +10380,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10389,7 +10401,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10398,7 +10410,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10406,10 +10418,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10527,10 +10539,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10650,10 +10662,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10676,19 +10688,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10737,7 +10749,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10758,7 +10770,7 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>83</v>
@@ -10767,7 +10779,7 @@
         <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>
@@ -10775,10 +10787,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10896,10 +10908,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11019,10 +11031,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11048,16 +11060,16 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11067,7 +11079,7 @@
         <v>83</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>83</v>
@@ -11106,7 +11118,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11121,13 +11133,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>83</v>
@@ -11136,7 +11148,7 @@
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>83</v>
@@ -11144,10 +11156,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11173,13 +11185,13 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11229,7 +11241,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11250,7 +11262,7 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>83</v>
@@ -11259,7 +11271,7 @@
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>83</v>
@@ -11267,10 +11279,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11296,14 +11308,14 @@
         <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11313,7 +11325,7 @@
         <v>83</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>83</v>
@@ -11352,7 +11364,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11367,13 +11379,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>83</v>
@@ -11382,7 +11394,7 @@
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
@@ -11390,10 +11402,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11419,14 +11431,14 @@
         <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11475,7 +11487,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11496,7 +11508,7 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>83</v>
@@ -11505,7 +11517,7 @@
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11513,10 +11525,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11539,19 +11551,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11600,7 +11612,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11621,7 +11633,7 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>83</v>
@@ -11630,7 +11642,7 @@
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>83</v>
@@ -11638,10 +11650,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11667,16 +11679,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11725,7 +11737,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11746,7 +11758,7 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>83</v>
@@ -11755,7 +11767,7 @@
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>83</v>
@@ -11763,10 +11775,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11792,16 +11804,16 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11811,10 +11823,10 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>83</v>
@@ -11850,7 +11862,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11865,13 +11877,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>83</v>
@@ -11880,7 +11892,7 @@
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>83</v>
@@ -11888,10 +11900,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11917,13 +11929,13 @@
         <v>151</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11937,7 +11949,7 @@
         <v>83</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>83</v>
@@ -11973,7 +11985,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11994,7 +12006,7 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>83</v>
@@ -12003,7 +12015,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12011,10 +12023,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12037,13 +12049,13 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12094,7 +12106,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12115,7 +12127,7 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>83</v>
@@ -12124,7 +12136,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12132,10 +12144,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12158,16 +12170,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12217,7 +12229,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12238,7 +12250,7 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>
@@ -12247,7 +12259,7 @@
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>83</v>
@@ -12255,10 +12267,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12281,70 +12293,70 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N78" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="R78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q78" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="R78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12365,13 +12377,13 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>155</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12382,10 +12394,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12408,19 +12420,19 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -12469,7 +12481,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12484,22 +12496,22 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>83</v>
@@ -12507,10 +12519,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12628,10 +12640,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12751,10 +12763,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12780,16 +12792,16 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12814,13 +12826,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12838,7 +12850,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12859,7 +12871,7 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
@@ -12868,7 +12880,7 @@
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>83</v>
@@ -12876,10 +12888,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12905,16 +12917,16 @@
         <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12963,7 +12975,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12984,7 +12996,7 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>83</v>
@@ -12993,7 +13005,7 @@
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>83</v>
@@ -13001,14 +13013,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13030,13 +13042,13 @@
         <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13086,7 +13098,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13095,7 +13107,7 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>103</v>
@@ -13107,7 +13119,7 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
@@ -13116,7 +13128,7 @@
         <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>83</v>
@@ -13124,14 +13136,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13153,13 +13165,13 @@
         <v>151</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13209,7 +13221,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13218,7 +13230,7 @@
         <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -13230,7 +13242,7 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>83</v>
@@ -13239,7 +13251,7 @@
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>83</v>
@@ -13247,10 +13259,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13276,10 +13288,10 @@
         <v>151</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13330,7 +13342,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13351,7 +13363,7 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>83</v>
@@ -13360,7 +13372,7 @@
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>83</v>
@@ -13368,10 +13380,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13397,10 +13409,10 @@
         <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13451,7 +13463,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13472,7 +13484,7 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>83</v>
@@ -13481,7 +13493,7 @@
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>83</v>
@@ -13489,10 +13501,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13515,17 +13527,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13574,7 +13586,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13595,7 +13607,7 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>83</v>
@@ -13604,7 +13616,7 @@
         <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>83</v>
@@ -13612,10 +13624,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13638,19 +13650,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13699,7 +13711,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13714,22 +13726,22 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13737,10 +13749,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13858,10 +13870,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13981,10 +13993,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14010,10 +14022,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14040,13 +14052,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -14064,7 +14076,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14073,7 +14085,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14085,7 +14097,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14094,7 +14106,7 @@
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14102,10 +14114,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14131,16 +14143,16 @@
         <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14189,7 +14201,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14210,7 +14222,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14219,7 +14231,7 @@
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14227,10 +14239,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14256,16 +14268,16 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14290,11 +14302,11 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14312,7 +14324,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14333,7 +14345,7 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>83</v>
@@ -14342,7 +14354,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14350,10 +14362,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14376,16 +14388,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14435,7 +14447,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14473,10 +14485,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14499,13 +14511,13 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14556,7 +14568,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14577,7 +14589,7 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>83</v>
@@ -14594,10 +14606,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14623,16 +14635,16 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14657,11 +14669,11 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14679,7 +14691,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14694,22 +14706,22 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14717,10 +14729,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14743,19 +14755,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14804,7 +14816,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14819,33 +14831,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14868,19 +14880,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14917,17 +14929,17 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14948,7 +14960,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>155</v>
@@ -14957,7 +14969,7 @@
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14965,13 +14977,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -14993,19 +15005,19 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15054,7 +15066,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15069,13 +15081,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>155</v>
@@ -15084,7 +15096,7 @@
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>83</v>
@@ -15092,13 +15104,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -15120,19 +15132,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15181,7 +15193,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15196,13 +15208,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>155</v>
@@ -15211,7 +15223,7 @@
         <v>83</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15219,10 +15231,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15245,19 +15257,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -15306,7 +15318,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15321,22 +15333,22 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>83</v>
@@ -15344,10 +15356,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15465,10 +15477,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15588,10 +15600,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15617,16 +15629,16 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15639,7 +15651,7 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>83</v>
@@ -15651,13 +15663,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15675,7 +15687,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15696,7 +15708,7 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>83</v>
@@ -15705,7 +15717,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15713,10 +15725,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15742,13 +15754,13 @@
         <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15762,7 +15774,7 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>83</v>
@@ -15774,13 +15786,13 @@
         <v>83</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -15798,7 +15810,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15819,7 +15831,7 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>83</v>
@@ -15828,7 +15840,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15836,10 +15848,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15865,16 +15877,16 @@
         <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15887,7 +15899,7 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>83</v>
@@ -15923,7 +15935,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15944,7 +15956,7 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>83</v>
@@ -15953,7 +15965,7 @@
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15961,10 +15973,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15990,10 +16002,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16008,7 +16020,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -16044,7 +16056,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16065,7 +16077,7 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16074,7 +16086,7 @@
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16082,14 +16094,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16111,10 +16123,10 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16129,7 +16141,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -16165,7 +16177,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16186,7 +16198,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>83</v>
@@ -16195,7 +16207,7 @@
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16203,14 +16215,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16232,13 +16244,13 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16252,7 +16264,7 @@
         <v>83</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>83</v>
@@ -16288,7 +16300,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16309,7 +16321,7 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16318,7 +16330,7 @@
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16326,14 +16338,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16355,10 +16367,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16385,13 +16397,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16409,7 +16421,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16430,7 +16442,7 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>83</v>
@@ -16439,7 +16451,7 @@
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16447,14 +16459,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16476,10 +16488,10 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16494,7 +16506,7 @@
         <v>83</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>83</v>
@@ -16530,7 +16542,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16551,7 +16563,7 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>83</v>
@@ -16560,7 +16572,7 @@
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16568,10 +16580,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16597,13 +16609,13 @@
         <v>151</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16653,7 +16665,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16674,7 +16686,7 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
@@ -16683,7 +16695,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16691,10 +16703,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16717,17 +16729,17 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16740,7 +16752,7 @@
         <v>83</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>83</v>
@@ -16776,7 +16788,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16797,7 +16809,7 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>83</v>
@@ -16806,7 +16818,7 @@
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16814,10 +16826,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16840,17 +16852,17 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16875,13 +16887,13 @@
         <v>83</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16899,7 +16911,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16920,16 +16932,16 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16937,10 +16949,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16963,19 +16975,19 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -17024,7 +17036,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17045,7 +17057,7 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>155</v>
@@ -17054,7 +17066,7 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17062,10 +17074,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17088,19 +17100,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17149,7 +17161,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17170,7 +17182,7 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>155</v>
@@ -17179,7 +17191,7 @@
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>83</v>
@@ -17187,10 +17199,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17213,19 +17225,19 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -17274,7 +17286,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17286,7 +17298,7 @@
         <v>83</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>83</v>
@@ -17295,7 +17307,7 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>155</v>
@@ -17312,10 +17324,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17433,10 +17445,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17556,14 +17568,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17585,16 +17597,16 @@
         <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -17643,7 +17655,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17681,10 +17693,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17707,17 +17719,17 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17742,13 +17754,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17766,7 +17778,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17787,7 +17799,7 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>155</v>
@@ -17796,7 +17808,7 @@
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17804,10 +17816,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17830,17 +17842,17 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17889,7 +17901,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17910,7 +17922,7 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>155</v>
@@ -17919,7 +17931,7 @@
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17927,10 +17939,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17953,19 +17965,19 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18014,7 +18026,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18035,7 +18047,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18044,7 +18056,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18052,10 +18064,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18078,17 +18090,17 @@
         <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18137,7 +18149,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18158,7 +18170,7 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>155</v>
@@ -18167,7 +18179,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18175,10 +18187,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18204,14 +18216,14 @@
         <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18236,31 +18248,31 @@
         <v>83</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18281,7 +18293,7 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>155</v>
@@ -18290,7 +18302,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18298,10 +18310,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18324,17 +18336,17 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
@@ -18383,7 +18395,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18392,7 +18404,7 @@
         <v>91</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>103</v>
@@ -18404,7 +18416,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18413,7 +18425,7 @@
         <v>83</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>83</v>
@@ -18421,10 +18433,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18447,13 +18459,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18504,7 +18516,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18525,7 +18537,7 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>155</v>
@@ -18542,10 +18554,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18568,19 +18580,19 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18629,7 +18641,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18650,10 +18662,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18667,10 +18679,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18788,10 +18800,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18911,14 +18923,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18940,16 +18952,16 @@
         <v>136</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -18998,7 +19010,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -19036,10 +19048,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19062,19 +19074,19 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19099,11 +19111,11 @@
         <v>83</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -19121,7 +19133,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>91</v>
@@ -19136,22 +19148,22 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19159,10 +19171,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19185,19 +19197,19 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -19246,7 +19258,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19267,16 +19279,16 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19284,14 +19296,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19310,16 +19322,16 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19369,7 +19381,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19390,7 +19402,7 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>155</v>
@@ -19399,7 +19411,7 @@
         <v>83</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>83</v>
@@ -19407,10 +19419,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19433,19 +19445,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19494,7 +19506,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19515,10 +19527,10 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>83</v>
@@ -19532,10 +19544,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19558,19 +19570,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -19619,7 +19631,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19640,7 +19652,7 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>155</v>
@@ -19657,10 +19669,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19778,10 +19790,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19901,14 +19913,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19930,16 +19942,16 @@
         <v>136</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19988,7 +20000,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20026,10 +20038,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20052,16 +20064,16 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20111,7 +20123,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -20132,7 +20144,7 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>155</v>
@@ -20141,7 +20153,7 @@
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>83</v>
@@ -20149,10 +20161,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20178,10 +20190,10 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20208,31 +20220,31 @@
         <v>83</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="Z142" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF142" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>91</v>
@@ -20253,7 +20265,7 @@
         <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>155</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -544,7 +544,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}VAERSPatient-1948:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}vaersp-12-1948:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
   </si>
   <si>
     <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native case not xsi:nil</t>
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VAERSPatient-1949:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}VAERSPatient-1950:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}VAERSPatient-1951:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}VAERSPatient-1952:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}VAERSPatient-1953:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}VAERSPatient-1954:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
+vaersp-12-1949:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}vaersp-12-1950:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}vaersp-12-1951:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}vaersp-12-1952:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}vaersp-12-1953:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1954:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
   </si>
   <si>
     <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" case not xsi:nil</t>
@@ -726,7 +726,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VAERSPatient-1955:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}VAERSPatient-1956:if not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}VAERSPatient-1957:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}VAERSPatient-1958:if not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
+vaersp-12-1955:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}vaersp-12-1956:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}vaersp-12-1957:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1958:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
   </si>
   <si>
     <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" case not xsi:nil</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$141</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5425" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5385" uniqueCount="786">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-patient</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-patient.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1705,22 +1705,10 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedInd, player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedTime</t>
   </si>
   <si>
     <t>PID-30  (bool) and PID-29 (datetime)</t>
-  </si>
-  <si>
-    <t>Patient.deceased[x]:deceasedBoolean</t>
-  </si>
-  <si>
-    <t>deceasedBoolean</t>
-  </si>
-  <si>
-    <t>1916: source value from ADERS - 21_Death case 21_DeathDt nil &amp; 21_Death =1</t>
   </si>
   <si>
     <t>Patient.deceased[x]:deceasedDateTime</t>
@@ -1733,7 +1721,7 @@
 </t>
   </si>
   <si>
-    <t>1917: source value from ADERS - 21_DeathDt case 21_DeathDt NOT nil</t>
+    <t>1917: source value from ADERS - 21_DeathDt</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2780,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP142"/>
+  <dimension ref="A1:AP141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.8515625" customWidth="true" bestFit="true"/>
@@ -14638,7 +14626,7 @@
         <v>82</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>545</v>
+        <v>139</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>538</v>
@@ -14659,7 +14647,7 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>154</v>
@@ -14668,7 +14656,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -14676,13 +14664,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>538</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>82</v>
@@ -14704,7 +14692,7 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>347</v>
+        <v>549</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>540</v>
@@ -14783,7 +14771,7 @@
         <v>550</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>154</v>
@@ -14792,7 +14780,7 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
@@ -14803,11 +14791,9 @@
         <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14816,31 +14802,31 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L101" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="M101" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14889,13 +14875,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14904,19 +14890,19 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>154</v>
+        <v>559</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14924,10 +14910,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14938,32 +14924,28 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>556</v>
+        <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>557</v>
+        <v>151</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -15011,34 +14993,34 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>555</v>
+        <v>153</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>154</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -15046,21 +15028,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -15072,15 +15054,17 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15117,31 +15101,31 @@
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -15164,44 +15148,46 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>158</v>
+        <v>564</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>159</v>
+        <v>565</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -15213,7 +15199,7 @@
         <v>82</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>82</v>
@@ -15225,49 +15211,49 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>162</v>
+        <v>571</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>154</v>
+        <v>425</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
@@ -15276,7 +15262,7 @@
         <v>82</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>82</v>
@@ -15284,10 +15270,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15304,7 +15290,7 @@
         <v>82</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
         <v>91</v>
@@ -15313,17 +15299,15 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15335,7 +15319,7 @@
         <v>82</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>82</v>
@@ -15350,10 +15334,10 @@
         <v>183</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15371,7 +15355,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15398,7 +15382,7 @@
         <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>82</v>
@@ -15406,10 +15390,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15432,18 +15416,20 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15455,7 +15441,7 @@
         <v>82</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>82</v>
@@ -15467,13 +15453,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15491,7 +15477,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15509,7 +15495,7 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
@@ -15518,7 +15504,7 @@
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>82</v>
@@ -15526,10 +15512,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15540,10 +15526,10 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15555,17 +15541,13 @@
         <v>150</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15577,7 +15559,7 @@
         <v>82</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>82</v>
@@ -15613,13 +15595,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15631,7 +15613,7 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>433</v>
+        <v>594</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
@@ -15640,7 +15622,7 @@
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
@@ -15648,21 +15630,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>91</v>
@@ -15677,10 +15659,10 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15695,7 +15677,7 @@
         <v>82</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>82</v>
@@ -15731,13 +15713,13 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>82</v>
@@ -15749,7 +15731,7 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
@@ -15758,7 +15740,7 @@
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>82</v>
@@ -15766,14 +15748,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15783,7 +15765,7 @@
         <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
@@ -15795,12 +15777,14 @@
         <v>150</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>608</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15813,7 +15797,7 @@
         <v>82</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>82</v>
@@ -15849,7 +15833,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15867,7 +15851,7 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
@@ -15876,7 +15860,7 @@
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>82</v>
@@ -15884,14 +15868,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15901,7 +15885,7 @@
         <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
@@ -15913,14 +15897,12 @@
         <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15933,7 +15915,7 @@
         <v>82</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>82</v>
@@ -15945,13 +15927,13 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15969,7 +15951,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15987,7 +15969,7 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
@@ -15996,7 +15978,7 @@
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>82</v>
@@ -16004,14 +15986,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16033,10 +16015,10 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16051,7 +16033,7 @@
         <v>82</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>82</v>
+        <v>626</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -16063,13 +16045,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -16087,7 +16069,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16105,7 +16087,7 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
@@ -16114,7 +16096,7 @@
         <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>82</v>
@@ -16122,14 +16104,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16139,7 +16121,7 @@
         <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
@@ -16151,12 +16133,14 @@
         <v>150</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16169,7 +16153,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -16205,7 +16189,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16223,7 +16207,7 @@
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
@@ -16232,7 +16216,7 @@
         <v>82</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>82</v>
@@ -16240,10 +16224,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16257,7 +16241,7 @@
         <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
@@ -16266,18 +16250,18 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>150</v>
+        <v>383</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -16289,7 +16273,7 @@
         <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>82</v>
@@ -16325,7 +16309,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16343,7 +16327,7 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>639</v>
+        <v>469</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>82</v>
@@ -16352,7 +16336,7 @@
         <v>82</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>82</v>
@@ -16360,10 +16344,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16377,26 +16361,26 @@
         <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16409,7 +16393,7 @@
         <v>82</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>645</v>
+        <v>82</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>82</v>
@@ -16421,13 +16405,13 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16445,7 +16429,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16463,16 +16447,16 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>469</v>
+        <v>650</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>82</v>
@@ -16480,10 +16464,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16506,17 +16490,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>291</v>
+        <v>654</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="O115" t="s" s="2">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16541,31 +16527,31 @@
         <v>82</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="Z115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16583,16 +16569,16 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>655</v>
+        <v>154</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>82</v>
@@ -16600,10 +16586,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16614,7 +16600,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16626,19 +16612,19 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16687,13 +16673,13 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>82</v>
@@ -16705,7 +16691,7 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>154</v>
@@ -16714,7 +16700,7 @@
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>82</v>
@@ -16722,10 +16708,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16748,19 +16734,19 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16809,7 +16795,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16821,13 +16807,13 @@
         <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>675</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>154</v>
@@ -16836,7 +16822,7 @@
         <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>82</v>
@@ -16844,10 +16830,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16858,7 +16844,7 @@
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>82</v>
@@ -16870,20 +16856,16 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>674</v>
+        <v>150</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>675</v>
+        <v>151</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>678</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16931,28 +16913,28 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>673</v>
+        <v>153</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>679</v>
+        <v>82</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>680</v>
+        <v>154</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -16966,21 +16948,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>82</v>
@@ -16992,15 +16974,17 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -17049,19 +17033,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -17084,14 +17068,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>157</v>
+        <v>680</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17104,24 +17088,26 @@
         <v>82</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>158</v>
+        <v>681</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>159</v>
+        <v>682</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17169,7 +17155,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>162</v>
+        <v>683</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17187,7 +17173,7 @@
         <v>82</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>82</v>
@@ -17204,14 +17190,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17224,13 +17210,13 @@
         <v>82</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>685</v>
@@ -17238,11 +17224,9 @@
       <c r="M121" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N121" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>267</v>
+        <v>687</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -17267,13 +17251,13 @@
         <v>82</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>82</v>
+        <v>688</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>82</v>
+        <v>689</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17291,7 +17275,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17303,22 +17287,22 @@
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>133</v>
+        <v>690</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>82</v>
@@ -17326,10 +17310,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17340,7 +17324,7 @@
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17352,17 +17336,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>291</v>
+        <v>406</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17387,37 +17371,37 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>688</v>
-      </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
@@ -17429,7 +17413,7 @@
         <v>82</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>694</v>
+        <v>412</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>154</v>
@@ -17438,7 +17422,7 @@
         <v>82</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>82</v>
@@ -17446,10 +17430,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17460,7 +17444,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -17472,17 +17456,19 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>406</v>
+        <v>472</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>699</v>
+        <v>476</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -17531,13 +17517,13 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>82</v>
@@ -17549,7 +17535,7 @@
         <v>82</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>154</v>
@@ -17558,7 +17544,7 @@
         <v>82</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>82</v>
@@ -17566,10 +17552,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17580,7 +17566,7 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
@@ -17592,19 +17578,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>472</v>
+        <v>552</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N124" t="s" s="2">
         <v>704</v>
       </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>476</v>
+        <v>705</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17653,13 +17637,13 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
@@ -17671,7 +17655,7 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>478</v>
+        <v>558</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>154</v>
@@ -17680,7 +17664,7 @@
         <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AP124" t="s" s="2">
         <v>82</v>
@@ -17688,10 +17672,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17714,10 +17698,10 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>556</v>
+        <v>110</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>707</v>
+        <v>519</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>708</v>
@@ -17749,13 +17733,13 @@
         <v>82</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>82</v>
+        <v>710</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>82</v>
+        <v>711</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
@@ -17773,7 +17757,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17791,7 +17775,7 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>562</v>
+        <v>250</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>154</v>
@@ -17800,7 +17784,7 @@
         <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>82</v>
@@ -17808,10 +17792,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17834,17 +17818,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>519</v>
+        <v>714</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17869,13 +17853,13 @@
         <v>82</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>714</v>
+        <v>82</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>715</v>
+        <v>82</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17893,7 +17877,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17902,7 +17886,7 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>82</v>
+        <v>717</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
@@ -17911,7 +17895,7 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>250</v>
+        <v>718</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>154</v>
@@ -17920,7 +17904,7 @@
         <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>82</v>
@@ -17928,10 +17912,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17954,18 +17938,16 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>720</v>
-      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
@@ -18013,7 +17995,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18022,7 +18004,7 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
@@ -18031,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>154</v>
@@ -18040,7 +18022,7 @@
         <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>723</v>
+        <v>82</v>
       </c>
       <c r="AP127" t="s" s="2">
         <v>82</v>
@@ -18062,7 +18044,7 @@
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
@@ -18074,7 +18056,7 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>383</v>
+        <v>670</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>725</v>
@@ -18082,8 +18064,12 @@
       <c r="M128" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+      <c r="N128" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -18137,7 +18123,7 @@
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>82</v>
@@ -18149,10 +18135,10 @@
         <v>82</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -18166,10 +18152,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18180,7 +18166,7 @@
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>82</v>
@@ -18192,20 +18178,16 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>674</v>
+        <v>150</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>729</v>
+        <v>151</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18253,28 +18235,28 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>728</v>
+        <v>153</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>733</v>
+        <v>154</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>734</v>
+        <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18288,21 +18270,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>82</v>
@@ -18314,15 +18296,17 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18371,19 +18355,19 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18406,14 +18390,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>157</v>
+        <v>680</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18426,24 +18410,26 @@
         <v>82</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>158</v>
+        <v>681</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>159</v>
+        <v>682</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="O131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18491,7 +18477,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>162</v>
+        <v>683</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18509,7 +18495,7 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
@@ -18526,45 +18512,45 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>685</v>
+        <v>735</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>686</v>
+        <v>736</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>160</v>
+        <v>737</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>267</v>
+        <v>738</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18589,13 +18575,11 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>82</v>
+        <v>739</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -18613,34 +18597,34 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>687</v>
+        <v>734</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>133</v>
+        <v>741</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>82</v>
+        <v>742</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>82</v>
+        <v>743</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>82</v>
@@ -18648,10 +18632,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18659,13 +18643,13 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
@@ -18674,19 +18658,19 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18711,11 +18695,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Y133" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z133" t="s" s="2">
-        <v>743</v>
+        <v>82</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18733,10 +18719,10 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>90</v>
@@ -18748,19 +18734,19 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>82</v>
@@ -18768,21 +18754,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>82</v>
+        <v>753</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18794,20 +18780,18 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>347</v>
+        <v>754</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>752</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18855,13 +18839,13 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
@@ -18873,16 +18857,16 @@
         <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>754</v>
+        <v>154</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>82</v>
@@ -18890,21 +18874,21 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>757</v>
+        <v>82</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18913,21 +18897,23 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>758</v>
+        <v>390</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>763</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>764</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -18975,13 +18961,13 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
@@ -18993,16 +18979,16 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>762</v>
+        <v>718</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>154</v>
+        <v>765</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>763</v>
+        <v>82</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>82</v>
@@ -19010,10 +18996,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19024,31 +19010,31 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J136" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>390</v>
+        <v>670</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -19097,13 +19083,13 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
@@ -19115,10 +19101,10 @@
         <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>722</v>
+        <v>771</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>769</v>
+        <v>154</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -19132,10 +19118,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19146,32 +19132,28 @@
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>674</v>
+        <v>150</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>771</v>
+        <v>151</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>774</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -19219,28 +19201,28 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>770</v>
+        <v>153</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>775</v>
+        <v>154</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -19254,21 +19236,21 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -19280,15 +19262,17 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19337,19 +19321,19 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>82</v>
@@ -19372,14 +19356,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>157</v>
+        <v>680</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19392,24 +19376,26 @@
         <v>82</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>158</v>
+        <v>681</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>159</v>
+        <v>682</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="O139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
@@ -19457,7 +19443,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>162</v>
+        <v>683</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19475,7 +19461,7 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>82</v>
@@ -19492,46 +19478,44 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>135</v>
+        <v>776</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>685</v>
+        <v>777</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>686</v>
+        <v>778</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>82</v>
       </c>
@@ -19579,34 +19563,34 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>687</v>
+        <v>775</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>82</v>
+        <v>780</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>82</v>
@@ -19614,10 +19598,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19640,17 +19624,15 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>780</v>
+        <v>110</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="N141" t="s" s="2">
         <v>783</v>
       </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19675,13 +19657,13 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>82</v>
+        <v>783</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>82</v>
+        <v>784</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19699,7 +19681,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19717,7 +19699,7 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>275</v>
+        <v>785</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>154</v>
@@ -19726,132 +19708,14 @@
         <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>784</v>
+        <v>82</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP142" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP142">
+  <autoFilter ref="A1:AP141">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19861,7 +19725,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI141">
+  <conditionalFormatting sqref="A2:AI140">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,10 +541,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}vaersp-12-1948:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
-  </si>
-  <si>
-    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native case not xsi:nil</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}vaersp-12-1948:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
+  </si>
+  <si>
+    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native if not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:ombCategory.id</t>
@@ -606,10 +606,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersp-12-1949:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}vaersp-12-1950:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}vaersp-12-1951:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}vaersp-12-1952:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}vaersp-12-1953:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1954:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
-  </si>
-  <si>
-    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" case not xsi:nil</t>
+vaersp-12-1949:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}vaersp-12-1950:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}vaersp-12-1951:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}vaersp-12-1952:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}vaersp-12-1953:If (null) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1954:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
+  </si>
+  <si>
+    <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" if not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:detailed</t>
@@ -723,10 +723,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersp-12-1955:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}vaersp-12-1956:null: if not xsi:nil then urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}vaersp-12-1957:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1958:null: if not xsi:nil then http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
-  </si>
-  <si>
-    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" case not xsi:nil</t>
+vaersp-12-1955:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}vaersp-12-1956:If (null) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}vaersp-12-1957:If (null) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1958:If (null) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
+  </si>
+  <si>
+    <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" if not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:detailed</t>
@@ -875,7 +875,7 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t>1863: source value from ADERS - 0_Pt_ICN_Full</t>
+    <t>1863: source value based on ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>id</t>
@@ -1639,7 +1639,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
   </si>
   <si>
-    <t>1880: source value from ADERS - 3_ptSex</t>
+    <t>1880: source value based on ADERS - 3_ptSex</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1667,7 +1667,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>1874: source value from ADERS - 2_ptDOB</t>
+    <t>1874: source value based on ADERS - 2_ptDOB</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1721,7 +1721,7 @@
 </t>
   </si>
   <si>
-    <t>1917: source value from ADERS - 21_DeathDt</t>
+    <t>1917: source value based on ADERS - 21_DeathDt</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2806,7 +2806,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="103.6484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="100.58984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="786">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,13 +543,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}vaersp-12-1948:If (24-1) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native {null}</t>
-  </si>
-  <si>
-    <t>1948: fixed value = urn:oid:2.16.840.1.113883.6.238#1002-5 American Indian or Alaska Native when ADERS - 24_PtRace_AIAN (24-1) if not xsi:nil</t>
-  </si>
-  <si>
     <t>Patient.extension:race.extension:ombCategory.id</t>
   </si>
   <si>
@@ -609,7 +602,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersp-12-1949:If (24-2) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {null}vaersp-12-1950:If (24-3) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {null}vaersp-12-1951:If (24-4) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {null}vaersp-12-1952:If (24-5) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {null}vaersp-12-1953:If (24-6) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1954:If (24-7) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {null}</t>
+vaersp-12-1948:If (24-1) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#1002-5 "American Indian or Alaska Native" {true}vaersp-12-1949:If (24-2) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2028-9 "Asian" {true}vaersp-12-1950:If (24-3) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2054-5 "Black or African American" {true}vaersp-12-1951:If (24-4) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2076-8 "Native Hawaiian or Other Pacific Islander" {true}vaersp-12-1952:If (24-5) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2106-3 "White" {true}vaersp-12-1953:If (24-6) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {true}vaersp-12-1954:If (24-7) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" {true}</t>
   </si>
   <si>
     <t>1954: fixed value = urn:oid:2.16.840.1.113883.6.238#2131-1 "Other Race" when ADERS - 24_PtRace_Other (24-7) if not xsi:nil</t>
@@ -726,7 +719,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vaersp-12-1955:If (25-1) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {null}vaersp-12-1956:If (25-2) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {null}vaersp-12-1957:If (25-3) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {null}vaersp-12-1958:If (25-4) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {null}</t>
+vaersp-12-1955:If (25-1) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2135-2 "Hispanic or Latino" {true}vaersp-12-1956:If (25-2) is not xsi:nil then fixed value urn:oid:2.16.840.1.113883.6.238#2186-5 "Not Hispanic or Latino" {true}vaersp-12-1957:If (25-3) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#UNK "unknown" {true}vaersp-12-1958:If (25-4) is not xsi:nil then fixed value http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" {true}</t>
   </si>
   <si>
     <t>1958: fixed value = http://terminology.hl7.org/CodeSystem/v3-NullFlavor#OTH "other" when ADERS - 25_PtEthnicity_Other (25-4) if not xsi:nil</t>
@@ -2812,7 +2805,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="135.9140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="131.8203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="45.03125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.8125" customWidth="true" bestFit="true"/>
@@ -4396,10 +4389,10 @@
         <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
@@ -4422,10 +4415,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4543,10 +4536,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4664,10 +4657,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4693,13 +4686,13 @@
         <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4749,7 +4742,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>91</v>
@@ -4787,10 +4780,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4813,13 +4806,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4846,46 +4839,46 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AK17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
@@ -4908,13 +4901,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>83</v>
@@ -4939,10 +4932,10 @@
         <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -5031,10 +5024,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5152,10 +5145,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5275,10 +5268,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5304,13 +5297,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5318,7 +5311,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -5360,7 +5353,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -5398,10 +5391,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5424,13 +5417,13 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5457,11 +5450,11 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -5479,7 +5472,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5517,13 +5510,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>83</v>
@@ -5548,10 +5541,10 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5640,10 +5633,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5761,10 +5754,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5884,10 +5877,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5913,13 +5906,13 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5927,7 +5920,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5969,7 +5962,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -6007,10 +6000,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6036,10 +6029,10 @@
         <v>151</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6090,7 +6083,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -6128,10 +6121,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6157,13 +6150,13 @@
         <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6171,7 +6164,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>83</v>
@@ -6213,7 +6206,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -6251,10 +6244,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6277,13 +6270,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6334,7 +6327,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6372,13 +6365,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>83</v>
@@ -6400,13 +6393,13 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6495,7 +6488,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>150</v>
@@ -6616,7 +6609,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>157</v>
@@ -6739,7 +6732,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>157</v>
@@ -6862,10 +6855,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6983,10 +6976,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7104,10 +7097,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7133,13 +7126,13 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7189,7 +7182,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>91</v>
@@ -7227,10 +7220,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7253,13 +7246,13 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7286,47 +7279,47 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
+      <c r="AL37" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>134</v>
@@ -7346,13 +7339,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>83</v>
@@ -7377,10 +7370,10 @@
         <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7469,10 +7462,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7590,10 +7583,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7713,10 +7706,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7742,13 +7735,13 @@
         <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7756,7 +7749,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>83</v>
@@ -7798,7 +7791,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7836,10 +7829,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7862,13 +7855,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7895,11 +7888,11 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7917,7 +7910,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7955,13 +7948,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>157</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -7986,10 +7979,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8078,10 +8071,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8199,10 +8192,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8322,10 +8315,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8351,13 +8344,13 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8365,7 +8358,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -8407,7 +8400,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -8445,10 +8438,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8474,10 +8467,10 @@
         <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8528,7 +8521,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8566,10 +8559,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8595,13 +8588,13 @@
         <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8609,7 +8602,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8651,7 +8644,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8689,10 +8682,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8715,13 +8708,13 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8772,7 +8765,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8810,13 +8803,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>83</v>
@@ -8838,16 +8831,16 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8918,7 +8911,7 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
@@ -8935,13 +8928,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>83</v>
@@ -8963,7 +8956,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>137</v>
@@ -9058,13 +9051,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>83</v>
@@ -9086,13 +9079,13 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9181,7 +9174,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>150</v>
@@ -9302,7 +9295,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>157</v>
@@ -9423,10 +9416,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9452,13 +9445,13 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9466,7 +9459,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>83</v>
@@ -9508,7 +9501,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -9546,10 +9539,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9575,10 +9568,10 @@
         <v>151</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9629,7 +9622,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9644,7 +9637,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
@@ -9667,10 +9660,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9696,16 +9689,16 @@
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9754,7 +9747,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9792,10 +9785,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9818,17 +9811,17 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9877,7 +9870,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9892,22 +9885,22 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9915,10 +9908,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10036,10 +10029,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10159,10 +10152,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10188,16 +10181,16 @@
         <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10222,31 +10215,31 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10267,7 +10260,7 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10284,10 +10277,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10310,19 +10303,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10347,31 +10340,31 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="Y62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10392,7 +10385,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10401,7 +10394,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10409,10 +10402,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10530,10 +10523,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10653,10 +10646,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10679,19 +10672,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10740,7 +10733,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10761,7 +10754,7 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>83</v>
@@ -10770,7 +10763,7 @@
         <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>
@@ -10778,10 +10771,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10899,10 +10892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11022,10 +11015,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11051,16 +11044,16 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11070,7 +11063,7 @@
         <v>83</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>83</v>
@@ -11109,7 +11102,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11124,22 +11117,22 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>83</v>
@@ -11147,10 +11140,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11176,13 +11169,13 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11232,7 +11225,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11253,7 +11246,7 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>83</v>
@@ -11262,7 +11255,7 @@
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>83</v>
@@ -11270,10 +11263,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11299,14 +11292,14 @@
         <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11316,7 +11309,7 @@
         <v>83</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>83</v>
@@ -11355,7 +11348,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11370,22 +11363,22 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
@@ -11393,10 +11386,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11422,14 +11415,14 @@
         <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11478,7 +11471,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11499,7 +11492,7 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>83</v>
@@ -11508,7 +11501,7 @@
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11516,10 +11509,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11542,19 +11535,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11603,7 +11596,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11624,7 +11617,7 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>83</v>
@@ -11633,7 +11626,7 @@
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>83</v>
@@ -11641,10 +11634,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11670,16 +11663,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11728,7 +11721,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11749,7 +11742,7 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>83</v>
@@ -11758,7 +11751,7 @@
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>83</v>
@@ -11766,10 +11759,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11795,16 +11788,16 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11814,46 +11807,46 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11868,22 +11861,22 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>83</v>
@@ -11891,10 +11884,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11920,13 +11913,13 @@
         <v>151</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11940,7 +11933,7 @@
         <v>83</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>83</v>
@@ -11976,7 +11969,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11997,7 +11990,7 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>83</v>
@@ -12006,7 +11999,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12014,10 +12007,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12040,13 +12033,13 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12097,7 +12090,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12118,7 +12111,7 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>83</v>
@@ -12127,7 +12120,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12135,10 +12128,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12161,16 +12154,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12220,7 +12213,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12241,7 +12234,7 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>
@@ -12250,7 +12243,7 @@
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>83</v>
@@ -12258,10 +12251,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12284,26 +12277,26 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="O78" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q78" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="R78" t="s" s="2">
         <v>83</v>
       </c>
@@ -12347,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12368,13 +12361,13 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>155</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12385,10 +12378,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12411,19 +12404,19 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -12472,7 +12465,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12487,22 +12480,22 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>83</v>
@@ -12510,10 +12503,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12631,10 +12624,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12754,10 +12747,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12783,16 +12776,16 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12817,31 +12810,31 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12862,7 +12855,7 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
@@ -12871,7 +12864,7 @@
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>83</v>
@@ -12879,10 +12872,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12908,16 +12901,16 @@
         <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12966,7 +12959,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12987,7 +12980,7 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>83</v>
@@ -12996,7 +12989,7 @@
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>83</v>
@@ -13004,14 +12997,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13033,13 +13026,13 @@
         <v>151</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13089,7 +13082,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13098,7 +13091,7 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>103</v>
@@ -13110,7 +13103,7 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
@@ -13119,7 +13112,7 @@
         <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>83</v>
@@ -13127,14 +13120,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13156,13 +13149,13 @@
         <v>151</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13212,7 +13205,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13221,7 +13214,7 @@
         <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -13233,7 +13226,7 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>83</v>
@@ -13242,7 +13235,7 @@
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>83</v>
@@ -13250,10 +13243,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13279,10 +13272,10 @@
         <v>151</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13333,7 +13326,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13354,7 +13347,7 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>83</v>
@@ -13363,7 +13356,7 @@
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>83</v>
@@ -13371,10 +13364,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13400,10 +13393,10 @@
         <v>151</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13454,7 +13447,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13475,7 +13468,7 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>83</v>
@@ -13484,7 +13477,7 @@
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>83</v>
@@ -13492,10 +13485,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13518,17 +13511,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13577,7 +13570,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13598,7 +13591,7 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>83</v>
@@ -13607,7 +13600,7 @@
         <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>83</v>
@@ -13615,10 +13608,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13641,19 +13634,19 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13702,7 +13695,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13717,22 +13710,22 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13740,10 +13733,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13861,10 +13854,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13984,10 +13977,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14013,10 +14006,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14043,40 +14036,40 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AG92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14088,7 +14081,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14097,7 +14090,7 @@
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14105,10 +14098,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14134,16 +14127,16 @@
         <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14192,7 +14185,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14213,7 +14206,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14222,7 +14215,7 @@
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14230,10 +14223,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14259,16 +14252,16 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14293,11 +14286,11 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -14315,7 +14308,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14336,7 +14329,7 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>83</v>
@@ -14345,7 +14338,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14353,10 +14346,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14379,16 +14372,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14438,7 +14431,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14476,10 +14469,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14502,13 +14495,13 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14559,7 +14552,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14580,7 +14573,7 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>83</v>
@@ -14597,10 +14590,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14626,16 +14619,16 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14660,11 +14653,11 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14682,7 +14675,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14697,22 +14690,22 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14720,10 +14713,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14746,19 +14739,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14807,7 +14800,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14822,33 +14815,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AQ98" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14871,19 +14864,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14920,7 +14913,7 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
@@ -14930,7 +14923,7 @@
         <v>140</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14951,7 +14944,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>155</v>
@@ -14960,7 +14953,7 @@
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14968,13 +14961,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -14996,19 +14989,19 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15057,7 +15050,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15072,13 +15065,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>155</v>
@@ -15087,7 +15080,7 @@
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>83</v>
@@ -15095,10 +15088,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15121,19 +15114,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15182,7 +15175,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15197,22 +15190,22 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15220,10 +15213,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15341,10 +15334,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15464,10 +15457,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15493,16 +15486,16 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15515,43 +15508,43 @@
         <v>83</v>
       </c>
       <c r="T104" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="U104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15572,7 +15565,7 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>83</v>
@@ -15581,7 +15574,7 @@
         <v>83</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>83</v>
@@ -15589,10 +15582,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15618,13 +15611,13 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15638,43 +15631,43 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="U105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y105" t="s" s="2">
+      <c r="AA105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15695,7 +15688,7 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>83</v>
@@ -15704,7 +15697,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15712,10 +15705,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15741,16 +15734,16 @@
         <v>151</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M106" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="O106" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15763,7 +15756,7 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>83</v>
@@ -15799,7 +15792,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15820,7 +15813,7 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>83</v>
@@ -15829,7 +15822,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15837,10 +15830,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15866,10 +15859,10 @@
         <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15884,7 +15877,7 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>83</v>
@@ -15920,7 +15913,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15941,7 +15934,7 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>83</v>
@@ -15950,7 +15943,7 @@
         <v>83</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15958,14 +15951,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15987,10 +15980,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16005,7 +15998,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -16041,7 +16034,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16062,7 +16055,7 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16071,7 +16064,7 @@
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16079,14 +16072,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16108,13 +16101,13 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -16128,7 +16121,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -16164,7 +16157,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16185,7 +16178,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>83</v>
@@ -16194,7 +16187,7 @@
         <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16202,14 +16195,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16231,10 +16224,10 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16261,31 +16254,31 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16306,7 +16299,7 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16315,7 +16308,7 @@
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16323,14 +16316,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16352,10 +16345,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16370,7 +16363,7 @@
         <v>83</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>83</v>
@@ -16406,7 +16399,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16427,7 +16420,7 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>83</v>
@@ -16436,7 +16429,7 @@
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16444,10 +16437,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16473,13 +16466,13 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16529,7 +16522,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16550,7 +16543,7 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>83</v>
@@ -16559,7 +16552,7 @@
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16567,10 +16560,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16593,17 +16586,17 @@
         <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16616,7 +16609,7 @@
         <v>83</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>83</v>
@@ -16652,7 +16645,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16673,7 +16666,7 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>83</v>
@@ -16682,7 +16675,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16690,10 +16683,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16716,17 +16709,17 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16751,13 +16744,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16775,7 +16768,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16796,16 +16789,16 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16813,10 +16806,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16839,19 +16832,19 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16900,7 +16893,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16921,7 +16914,7 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>155</v>
@@ -16930,7 +16923,7 @@
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16938,10 +16931,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16964,19 +16957,19 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -17025,7 +17018,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17046,7 +17039,7 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>155</v>
@@ -17055,7 +17048,7 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17063,10 +17056,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17089,19 +17082,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17150,7 +17143,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17162,7 +17155,7 @@
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
@@ -17171,7 +17164,7 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>155</v>
@@ -17188,10 +17181,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17309,10 +17302,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17432,14 +17425,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17461,16 +17454,16 @@
         <v>136</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
@@ -17519,7 +17512,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17557,10 +17550,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17583,17 +17576,17 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -17618,13 +17611,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -17642,7 +17635,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17663,7 +17656,7 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>155</v>
@@ -17672,7 +17665,7 @@
         <v>83</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>83</v>
@@ -17680,10 +17673,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17706,17 +17699,17 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17765,7 +17758,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17786,7 +17779,7 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>155</v>
@@ -17795,7 +17788,7 @@
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17803,10 +17796,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17829,19 +17822,19 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M123" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>702</v>
-      </c>
       <c r="O123" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17890,7 +17883,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17911,7 +17904,7 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>155</v>
@@ -17920,7 +17913,7 @@
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17928,10 +17921,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17954,17 +17947,17 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18013,7 +18006,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18034,7 +18027,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18043,7 +18036,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18051,10 +18044,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18080,14 +18073,14 @@
         <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18112,13 +18105,13 @@
         <v>83</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -18136,7 +18129,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18157,7 +18150,7 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>155</v>
@@ -18166,7 +18159,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18174,10 +18167,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18200,17 +18193,17 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18259,7 +18252,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18268,7 +18261,7 @@
         <v>91</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>103</v>
@@ -18280,7 +18273,7 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>155</v>
@@ -18289,7 +18282,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18297,10 +18290,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18323,13 +18316,13 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18380,7 +18373,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18401,7 +18394,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18418,10 +18411,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18444,19 +18437,19 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -18505,7 +18498,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18526,10 +18519,10 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
@@ -18543,10 +18536,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18664,10 +18657,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18787,14 +18780,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18816,16 +18809,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18874,7 +18867,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18912,10 +18905,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18938,19 +18931,19 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -18975,11 +18968,11 @@
         <v>83</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -18997,7 +18990,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>91</v>
@@ -19012,22 +19005,22 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM132" t="s" s="2">
+      <c r="AO132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP132" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>83</v>
@@ -19035,10 +19028,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19061,19 +19054,19 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19122,7 +19115,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19143,16 +19136,16 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP133" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19160,14 +19153,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -19186,16 +19179,16 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -19245,7 +19238,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19266,7 +19259,7 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>155</v>
@@ -19275,7 +19268,7 @@
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19283,10 +19276,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19309,19 +19302,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>83</v>
@@ -19370,7 +19363,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19391,10 +19384,10 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>83</v>
@@ -19408,10 +19401,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19434,19 +19427,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19495,7 +19488,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19516,7 +19509,7 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>155</v>
@@ -19533,10 +19526,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19654,10 +19647,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19777,14 +19770,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19806,16 +19799,16 @@
         <v>136</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>161</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>83</v>
@@ -19864,7 +19857,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19902,10 +19895,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19928,16 +19921,16 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19987,7 +19980,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>91</v>
@@ -20008,7 +20001,7 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>155</v>
@@ -20017,7 +20010,7 @@
         <v>83</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>83</v>
@@ -20025,10 +20018,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20054,10 +20047,10 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -20084,13 +20077,13 @@
         <v>83</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>83</v>
@@ -20108,7 +20101,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -20129,7 +20122,7 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>155</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="785">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -641,12 +641,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>Race Text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the race concept(s).</t>
-  </si>
-  <si>
     <t>Patient.extension:race.extension:text.id</t>
   </si>
   <si>
@@ -657,6 +651,13 @@
   </si>
   <si>
     <t>Patient.extension:race.extension:text.value[x]</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersp-12-1948-1:If not xsi:nil then fixed value AIAN {true}vaersp-12-1949-1:If not xsi:nil then fixed value Asian {true}vaersp-12-1950-1:If not xsi:nil then fixed value BlkAM {true}vaersp-12-1951-1:If not xsi:nil then fixed value NH_OPI {true}vaersp-12-1952-1:If not xsi:nil then fixed value White {true}vaersp-12-1953-1:If not xsi:nil then fixed value Unk {true}vaersp-12-1954-1:If not xsi:nil then fixed value Other {true}</t>
+  </si>
+  <si>
+    <t>1954-1: fixed value = Other if not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:race.url</t>
@@ -755,12 +756,6 @@
     <t>Patient.extension:ethnicity.extension:text</t>
   </si>
   <si>
-    <t>ethnicity Text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the ethnicity concept(s).</t>
-  </si>
-  <si>
     <t>Patient.extension:ethnicity.extension:text.id</t>
   </si>
   <si>
@@ -771,6 +766,13 @@
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:text.value[x]</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vaersp-12-1955-1:If not xsi:nil then fixed value HispLat {true}vaersp-12-1956-1:If not xsi:nil then fixed value NHL {true}vaersp-12-1957-1:If not xsi:nil then fixed value Unk {true}vaersp-12-1958-1:If not xsi:nil then fixed value Other {true}</t>
+  </si>
+  <si>
+    <t>1958-1: fixed value = Other if not xsi:nil</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.url</t>
@@ -874,9 +876,6 @@
     <t>Patients are almost always assigned specific numerical identifiers.</t>
   </si>
   <si>
-    <t>1863: source value based on ADERS - 0_Pt_ICN_Full (0)</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -1192,6 +1191,9 @@
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1863: source value based on ADERS - 0_Pt_ICN_Full (0)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -1493,9 +1495,6 @@
   </si>
   <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
-  </si>
-  <si>
-    <t>2023: target not supported</t>
   </si>
   <si>
     <t>telecom</t>
@@ -5541,10 +5540,10 @@
         <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5633,7 +5632,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>168</v>
@@ -5754,21 +5753,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -5783,14 +5782,12 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5860,7 +5857,7 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>83</v>
@@ -5877,7 +5874,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>172</v>
@@ -6000,7 +5997,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>178</v>
@@ -6017,7 +6014,7 @@
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -6095,10 +6092,10 @@
         <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
@@ -7979,10 +7976,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>168</v>
@@ -8192,21 +8189,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>170</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -8221,14 +8218,12 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8298,7 +8293,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -8315,7 +8310,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>172</v>
@@ -8438,7 +8433,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>178</v>
@@ -8455,7 +8450,7 @@
         <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>83</v>
@@ -8533,10 +8528,10 @@
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
@@ -9885,22 +9880,22 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9908,10 +9903,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10029,10 +10024,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10152,10 +10147,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10181,16 +10176,16 @@
         <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10218,28 +10213,28 @@
         <v>182</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Z61" t="s" s="2">
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10260,7 +10255,7 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10277,10 +10272,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10303,19 +10298,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10340,31 +10335,31 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="Z62" t="s" s="2">
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10385,7 +10380,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10394,7 +10389,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10402,10 +10397,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10523,10 +10518,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10646,10 +10641,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10675,16 +10670,16 @@
         <v>179</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10733,7 +10728,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10754,16 +10749,16 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>
@@ -10771,10 +10766,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10892,10 +10887,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11015,10 +11010,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11044,16 +11039,16 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11063,46 +11058,46 @@
         <v>83</v>
       </c>
       <c r="S68" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11117,22 +11112,22 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>83</v>
@@ -11140,10 +11135,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11169,13 +11164,13 @@
         <v>151</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11225,7 +11220,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11246,16 +11241,16 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>83</v>
@@ -11263,10 +11258,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11292,14 +11287,14 @@
         <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11309,46 +11304,46 @@
         <v>83</v>
       </c>
       <c r="S70" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11363,22 +11358,22 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
@@ -11386,10 +11381,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11415,14 +11410,14 @@
         <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11471,7 +11466,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11492,16 +11487,16 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11509,10 +11504,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11535,19 +11530,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11596,7 +11591,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11617,16 +11612,16 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>83</v>
@@ -11634,10 +11629,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11663,16 +11658,16 @@
         <v>151</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11721,7 +11716,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11742,16 +11737,16 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>83</v>
@@ -11759,10 +11754,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11788,16 +11783,16 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11807,46 +11802,46 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="T74" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="T74" t="s" s="2">
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11861,22 +11856,22 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>83</v>
@@ -11884,10 +11879,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11913,13 +11908,13 @@
         <v>151</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11933,43 +11928,43 @@
         <v>83</v>
       </c>
       <c r="T75" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11984,7 +11979,7 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>83</v>
@@ -12277,7 +12272,7 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>398</v>
@@ -13710,22 +13705,22 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13733,10 +13728,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13854,10 +13849,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13977,10 +13972,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14006,10 +14001,10 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14039,37 +14034,37 @@
         <v>182</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="Z92" t="s" s="2">
+      <c r="AA92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AA92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF92" t="s" s="2">
+      <c r="AG92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14081,16 +14076,16 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>83</v>
@@ -14098,10 +14093,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14127,16 +14122,16 @@
         <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14185,7 +14180,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14206,16 +14201,16 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>83</v>
@@ -14223,10 +14218,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14252,16 +14247,16 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14290,25 +14285,25 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14338,7 +14333,7 @@
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>83</v>
@@ -14346,10 +14341,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14372,16 +14367,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14431,7 +14426,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14469,10 +14464,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14498,10 +14493,10 @@
         <v>383</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14552,7 +14547,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14590,10 +14585,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14619,16 +14614,16 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14657,7 +14652,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14675,7 +14670,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14690,7 +14685,7 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
@@ -14699,13 +14694,13 @@
         <v>250</v>
       </c>
       <c r="AN97" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>83</v>
@@ -14713,10 +14708,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14739,19 +14734,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14800,7 +14795,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14815,33 +14810,33 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
+      <c r="AQ98" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>537</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14864,19 +14859,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14913,7 +14908,7 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
@@ -14923,7 +14918,7 @@
         <v>140</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14944,7 +14939,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>155</v>
@@ -14953,7 +14948,7 @@
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>83</v>
@@ -14961,13 +14956,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
@@ -14989,19 +14984,19 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -15050,7 +15045,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -15065,13 +15060,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>155</v>
@@ -15080,7 +15075,7 @@
         <v>83</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>83</v>
@@ -15088,10 +15083,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15114,19 +15109,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -15175,7 +15170,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15190,22 +15185,22 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>83</v>
@@ -15213,10 +15208,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15334,10 +15329,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15457,10 +15452,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15486,16 +15481,16 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15508,7 +15503,7 @@
         <v>83</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>83</v>
@@ -15523,28 +15518,28 @@
         <v>182</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15574,7 +15569,7 @@
         <v>83</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>83</v>
@@ -15582,10 +15577,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15611,13 +15606,13 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15631,7 +15626,7 @@
         <v>83</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>83</v>
@@ -15646,28 +15641,28 @@
         <v>182</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="Z105" t="s" s="2">
+      <c r="AA105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15697,7 +15692,7 @@
         <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>83</v>
@@ -15705,10 +15700,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15734,13 +15729,13 @@
         <v>151</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>431</v>
@@ -15756,43 +15751,43 @@
         <v>83</v>
       </c>
       <c r="T106" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15822,7 +15817,7 @@
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>83</v>
@@ -15830,10 +15825,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15859,10 +15854,10 @@
         <v>151</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15877,43 +15872,43 @@
         <v>83</v>
       </c>
       <c r="T107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15934,16 +15929,16 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>83</v>
@@ -15951,14 +15946,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15980,10 +15975,10 @@
         <v>151</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15998,43 +15993,43 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16055,16 +16050,16 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP108" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>83</v>
@@ -16072,14 +16067,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16101,13 +16096,13 @@
         <v>151</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -16121,43 +16116,43 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16178,16 +16173,16 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP109" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>83</v>
@@ -16195,14 +16190,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16224,10 +16219,10 @@
         <v>151</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16254,31 +16249,31 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="Z110" t="s" s="2">
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16299,16 +16294,16 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP110" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>83</v>
@@ -16316,14 +16311,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16345,10 +16340,10 @@
         <v>151</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16363,43 +16358,43 @@
         <v>83</v>
       </c>
       <c r="T111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16420,16 +16415,16 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP111" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>83</v>
@@ -16437,10 +16432,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16466,13 +16461,13 @@
         <v>151</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16522,7 +16517,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16543,16 +16538,16 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>83</v>
@@ -16560,10 +16555,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16589,14 +16584,14 @@
         <v>383</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16609,43 +16604,43 @@
         <v>83</v>
       </c>
       <c r="T113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16675,7 +16670,7 @@
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>83</v>
@@ -16683,10 +16678,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16709,17 +16704,17 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16744,14 +16739,14 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>649</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
       </c>
@@ -16768,7 +16763,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16789,16 +16784,16 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>83</v>
@@ -16806,10 +16801,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16832,19 +16827,19 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16893,7 +16888,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16914,7 +16909,7 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>155</v>
@@ -16923,7 +16918,7 @@
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>83</v>
@@ -16931,10 +16926,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16957,19 +16952,19 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -17018,7 +17013,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17039,7 +17034,7 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>155</v>
@@ -17048,7 +17043,7 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>83</v>
@@ -17056,10 +17051,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17082,19 +17077,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -17143,7 +17138,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17155,16 +17150,16 @@
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>155</v>
@@ -17181,10 +17176,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17302,10 +17297,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17425,14 +17420,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17454,10 +17449,10 @@
         <v>136</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>161</v>
@@ -17512,7 +17507,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17550,10 +17545,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17576,17 +17571,17 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -17611,14 +17606,14 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="Z121" t="s" s="2">
-        <v>689</v>
-      </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
       </c>
@@ -17635,7 +17630,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17656,7 +17651,7 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>155</v>
@@ -17665,7 +17660,7 @@
         <v>83</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>83</v>
@@ -17673,10 +17668,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17702,14 +17697,14 @@
         <v>406</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17758,7 +17753,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17788,7 +17783,7 @@
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>83</v>
@@ -17796,10 +17791,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17825,13 +17820,13 @@
         <v>472</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>476</v>
@@ -17883,7 +17878,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17904,7 +17899,7 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>155</v>
@@ -17913,7 +17908,7 @@
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>83</v>
@@ -17921,10 +17916,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17947,17 +17942,17 @@
         <v>83</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -18006,7 +18001,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18027,7 +18022,7 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>155</v>
@@ -18036,7 +18031,7 @@
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>83</v>
@@ -18044,10 +18039,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18073,14 +18068,14 @@
         <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -18108,11 +18103,11 @@
         <v>182</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="Z125" t="s" s="2">
-        <v>711</v>
-      </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
       </c>
@@ -18129,7 +18124,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18159,7 +18154,7 @@
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>83</v>
@@ -18167,10 +18162,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18196,14 +18191,14 @@
         <v>390</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -18252,7 +18247,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18261,7 +18256,7 @@
         <v>91</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>103</v>
@@ -18273,7 +18268,7 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>155</v>
@@ -18282,7 +18277,7 @@
         <v>83</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>83</v>
@@ -18290,10 +18285,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18319,10 +18314,10 @@
         <v>383</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18373,7 +18368,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18394,7 +18389,7 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>155</v>
@@ -18411,10 +18406,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18437,19 +18432,19 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -18498,7 +18493,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18519,10 +18514,10 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
@@ -18536,10 +18531,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18657,10 +18652,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18780,14 +18775,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18809,10 +18804,10 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>161</v>
@@ -18867,7 +18862,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18905,10 +18900,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18931,19 +18926,19 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -18968,11 +18963,11 @@
         <v>83</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
@@ -18990,7 +18985,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>91</v>
@@ -19005,22 +19000,22 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM132" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM132" t="s" s="2">
+      <c r="AN132" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="AN132" t="s" s="2">
+      <c r="AO132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP132" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>83</v>
@@ -19028,10 +19023,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19054,19 +19049,19 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>745</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -19115,7 +19110,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19136,16 +19131,16 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="AN133" t="s" s="2">
+      <c r="AO133" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP133" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>83</v>
@@ -19153,14 +19148,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -19179,16 +19174,16 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -19238,7 +19233,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19259,7 +19254,7 @@
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>155</v>
@@ -19268,7 +19263,7 @@
         <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>83</v>
@@ -19276,10 +19271,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19305,16 +19300,16 @@
         <v>390</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>761</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>83</v>
@@ -19363,7 +19358,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19384,10 +19379,10 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>83</v>
@@ -19401,10 +19396,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19427,19 +19422,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
@@ -19488,7 +19483,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19509,7 +19504,7 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>155</v>
@@ -19526,10 +19521,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19647,10 +19642,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19770,14 +19765,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19799,10 +19794,10 @@
         <v>136</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>161</v>
@@ -19857,7 +19852,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19895,10 +19890,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19921,16 +19916,16 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19980,7 +19975,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>91</v>
@@ -20001,7 +19996,7 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>155</v>
@@ -20010,7 +20005,7 @@
         <v>83</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>83</v>
@@ -20018,10 +20013,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20047,10 +20042,10 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -20080,11 +20075,11 @@
         <v>182</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>784</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>83</v>
       </c>
@@ -20101,7 +20096,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -20122,7 +20117,7 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>155</v>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSPatient.xlsx
+++ b/docs/StructureDefinition-VAERSPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
